--- a/SAM_Opportunities_Report_20260624_PM.xlsx
+++ b/SAM_Opportunities_Report_20260624_PM.xlsx
@@ -14,10 +14,10 @@
     <sheet name="🔧 Specialty Pipeline" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$129</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🔴 Action Required'!$B$5:$N$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'👀 Watch List'!$B$5:$K$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'📋 Full Pipeline'!$B$5:$K$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'🔧 Specialty Pipeline'!$B$5:$K$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -855,22 +855,22 @@
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>$4.2B</t>
+          <t>$4.3B</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F26" s="26" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="F27" s="27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F38" s="26" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="F39" s="27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
     <row r="46" ht="20" customHeight="1">
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>→  54 active Solicitation(s) due within 14 days — immediate bid/no-bid decisions required.</t>
+          <t>→  53 active Solicitation(s) due within 14 days — immediate bid/no-bid decisions required.</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N92"/>
+  <dimension ref="B2:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1336,7 +1336,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>All open Solicitations sorted by urgency  ·  87 records  ·  As of June 24, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
+          <t>All open Solicitations sorted by urgency  ·  88 records  ·  As of June 24, 2026  ·  ★ Gold rows = SDVOSB set-aside</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>W911WN26BA014</t>
+          <t>12FPC326B0006</t>
         </is>
       </c>
       <c r="D22" s="40" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Madison, Ohio</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>12FPC326B0006</t>
+          <t>FA481426Q0026</t>
         </is>
       </c>
       <c r="D23" s="37" t="inlineStr">
         <is>
-          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>Madison, Ohio</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -2622,17 +2622,17 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>FA481426Q0026</t>
+          <t>W912ES26QA067</t>
         </is>
       </c>
       <c r="D24" s="40" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Fiber Optic Cable Replacement</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -2682,47 +2682,47 @@
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>W912ES26QA067</t>
-        </is>
-      </c>
-      <c r="D25" s="37" t="inlineStr">
-        <is>
-          <t>Fiber Optic Cable Replacement</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>36C25226Q0526</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>Madison, Wisconsin</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="G25" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="J25" s="20" t="inlineStr">
+      <c r="J25" s="23" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
@@ -2732,17 +2732,17 @@
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="39" t="inlineStr">
+      <c r="L25" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -2756,22 +2756,22 @@
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>36C25226Q0526</t>
+          <t>36C78626B0007</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
         <is>
-          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
+          <t>Y1PZ--810CM3033 Gravesite Expansion with FCA Deficiencies at  Dayton National Cemetery</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>Madison, Wisconsin</t>
+          <t>Dayton, Ohio</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G26" s="34" t="inlineStr">
@@ -2816,49 +2816,49 @@
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>36C78626B0007</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="inlineStr">
-        <is>
-          <t>Y1PZ--810CM3033 Gravesite Expansion with FCA Deficiencies at  Dayton National Cemetery</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>Dayton, Ohio</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="G27" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H27" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="23" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>5d</t>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>140P9726R0002</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
+        <is>
+          <t>Y--GLBA REHAB WATERLINE</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>Jul 01, 2026</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>6d</t>
         </is>
       </c>
       <c r="K27" s="18" t="inlineStr">
@@ -2866,17 +2866,17 @@
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L27" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M27" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N27" s="36" t="inlineStr">
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>140P9726R0002</t>
+          <t>140A1626QD002</t>
         </is>
       </c>
       <c r="D28" s="40" t="inlineStr">
         <is>
-          <t>Y--GLBA REHAB WATERLINE</t>
+          <t>N-- AIRR Security Cameras &amp; Badging for BTFA</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>140A1626QD002</t>
+          <t>140P6426B0004</t>
         </is>
       </c>
       <c r="D29" s="37" t="inlineStr">
         <is>
-          <t>N-- AIRR Security Cameras &amp; Badging for BTFA</t>
+          <t>Z--Munising Falls Trail Rehabilitation</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -3024,22 +3024,22 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>140P6426B0004</t>
+          <t>140P6026B0004</t>
         </is>
       </c>
       <c r="D30" s="40" t="inlineStr">
         <is>
-          <t>Z--Munising Falls Trail Rehabilitation</t>
+          <t>Z--BRVB - Entry Courtyard Improvements</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Topeka, Kansas</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>Jul 01, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="K30" s="18" t="inlineStr">
@@ -3091,22 +3091,22 @@
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>140P6026B0004</t>
+          <t>140P8326Q0042</t>
         </is>
       </c>
       <c r="D31" s="37" t="inlineStr">
         <is>
-          <t>Z--BRVB - Entry Courtyard Improvements</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>Topeka, Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0042</t>
+          <t>1305M326Q0251</t>
         </is>
       </c>
       <c r="D32" s="40" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>NOAA Western Regional Center H32 Electrical Repair</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>1305M326Q0251</t>
+          <t>140FC226Q0036</t>
         </is>
       </c>
       <c r="D33" s="37" t="inlineStr">
         <is>
-          <t>NOAA Western Regional Center H32 Electrical Repair</t>
+          <t>VY-MISSISQUOI NWR-PARKING LOT MAINT</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -3250,17 +3250,17 @@
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jul 03, 2026</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="K33" s="18" t="inlineStr">
@@ -3292,22 +3292,22 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>140FC226Q0036</t>
+          <t>FA469026Q0030</t>
         </is>
       </c>
       <c r="D34" s="40" t="inlineStr">
         <is>
-          <t>VY-MISSISQUOI NWR-PARKING LOT MAINT</t>
+          <t>Video Intercom System</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Ellsworth AFB, South Dakota</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000068</t>
+          <t>W911WN26BA014</t>
         </is>
       </c>
       <c r="D67" s="37" t="inlineStr">
         <is>
-          <t>Beresford Substation Stage 11, South Dakota</t>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G67" s="20" t="inlineStr">
@@ -5528,17 +5528,17 @@
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 14, 2026</t>
         </is>
       </c>
       <c r="J67" s="20" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="K67" s="43" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="D68" s="40" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
@@ -5637,22 +5637,22 @@
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>75F40126R00051</t>
+          <t>140L3626Q0032</t>
         </is>
       </c>
       <c r="D69" s="37" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G69" s="20" t="inlineStr">
@@ -5704,22 +5704,22 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>140P2026R0011</t>
+          <t>75F40126R00051</t>
         </is>
       </c>
       <c r="D70" s="40" t="inlineStr">
         <is>
-          <t>GLCA Hite</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>W9127826RA059</t>
+          <t>140P2026R0011</t>
         </is>
       </c>
       <c r="D71" s="37" t="inlineStr">
         <is>
-          <t>Water Tank Storage</t>
+          <t>GLCA Hite</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G71" s="20" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="K71" s="43" t="inlineStr">
@@ -5838,194 +5838,194 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
+          <t>W9127826RA059</t>
+        </is>
+      </c>
+      <c r="D72" s="40" t="inlineStr">
+        <is>
+          <t>Water Tank Storage</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>Jul 16, 2026</t>
+        </is>
+      </c>
+      <c r="J72" s="17" t="inlineStr">
+        <is>
+          <t>21d</t>
+        </is>
+      </c>
+      <c r="K72" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L72" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
           <t>W912HN26BA008</t>
         </is>
       </c>
-      <c r="D72" s="40" t="inlineStr">
+      <c r="D73" s="37" t="inlineStr">
         <is>
           <t>FY26 Brunswick Inner Harbor Dredging Project</t>
         </is>
       </c>
-      <c r="E72" s="17" t="inlineStr">
+      <c r="E73" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F72" s="17" t="inlineStr">
+      <c r="F73" s="20" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="G72" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H72" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="17" t="inlineStr">
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr">
         <is>
           <t>Jul 17, 2026</t>
         </is>
       </c>
-      <c r="J72" s="17" t="inlineStr">
+      <c r="J73" s="20" t="inlineStr">
         <is>
           <t>22d</t>
         </is>
       </c>
-      <c r="K72" s="43" t="inlineStr">
+      <c r="K73" s="43" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L72" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="32" customHeight="1">
-      <c r="B73" s="33" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="C73" s="23" t="inlineStr">
+      <c r="L73" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="32" customHeight="1">
+      <c r="B74" s="33" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="C74" s="23" t="inlineStr">
         <is>
           <t>W50S6T26QA026</t>
         </is>
       </c>
-      <c r="D73" s="28" t="inlineStr">
+      <c r="D74" s="28" t="inlineStr">
         <is>
           <t>Remove Traffic Island and Construct Sloped Concrete Static Display</t>
         </is>
       </c>
-      <c r="E73" s="23" t="inlineStr">
+      <c r="E74" s="23" t="inlineStr">
         <is>
           <t>California</t>
         </is>
       </c>
-      <c r="F73" s="23" t="inlineStr">
+      <c r="F74" s="23" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="G73" s="34" t="inlineStr">
+      <c r="G74" s="34" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="H73" s="23" t="inlineStr">
+      <c r="H74" s="23" t="inlineStr">
         <is>
           <t>$25K</t>
         </is>
       </c>
-      <c r="I73" s="23" t="inlineStr">
+      <c r="I74" s="23" t="inlineStr">
         <is>
           <t>Jul 17, 2026</t>
         </is>
       </c>
-      <c r="J73" s="23" t="inlineStr">
+      <c r="J74" s="23" t="inlineStr">
         <is>
           <t>22d</t>
         </is>
       </c>
-      <c r="K73" s="43" t="inlineStr">
+      <c r="K74" s="43" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L73" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="36" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="32" customHeight="1">
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
-        <is>
-          <t>FA301626B0001</t>
-        </is>
-      </c>
-      <c r="D74" s="40" t="inlineStr">
-        <is>
-          <t>Repair Carswell Ave.</t>
-        </is>
-      </c>
-      <c r="E74" s="17" t="inlineStr">
-        <is>
-          <t>DWG, Texas</t>
-        </is>
-      </c>
-      <c r="F74" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H74" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>Jul 17, 2026</t>
-        </is>
-      </c>
-      <c r="J74" s="17" t="inlineStr">
-        <is>
-          <t>22d</t>
-        </is>
-      </c>
-      <c r="K74" s="43" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L74" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="42" t="inlineStr">
+      <c r="L74" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -6039,22 +6039,22 @@
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>140P8326Q0046</t>
+          <t>FA301626B0001</t>
         </is>
       </c>
       <c r="D75" s="37" t="inlineStr">
         <is>
-          <t>LARO-DRILL NEW WATER WELL - SHERMAN HOMES CABINS</t>
+          <t>Repair Carswell Ave.</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>DWG, Texas</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G75" s="20" t="inlineStr">
@@ -6106,17 +6106,17 @@
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>75H70126R00030</t>
+          <t>140P8326Q0046</t>
         </is>
       </c>
       <c r="D76" s="40" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>LARO-DRILL NEW WATER WELL - SHERMAN HOMES CABINS</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
-          <t>Jul 20, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="J76" s="17" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="K76" s="43" t="inlineStr">
@@ -6173,22 +6173,22 @@
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>693C73-26-R-000047</t>
+          <t>75H70126R00030</t>
         </is>
       </c>
       <c r="D77" s="37" t="inlineStr">
         <is>
-          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
+          <t>Rosebud Lift Station Construction</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Rosebud, South Dakota</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="G77" s="20" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
-          <t>$12.9M</t>
+          <t>$11.8M</t>
         </is>
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>Jul 21, 2026</t>
+          <t>Jul 20, 2026</t>
         </is>
       </c>
       <c r="J77" s="20" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="K77" s="43" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>W912ES26BA013</t>
+          <t>693C73-26-R-000047</t>
         </is>
       </c>
       <c r="D78" s="40" t="inlineStr">
         <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G78" s="17" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$12.9M</t>
         </is>
       </c>
       <c r="I78" s="17" t="inlineStr">
@@ -6307,127 +6307,127 @@
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
+          <t>W912ES26BA013</t>
+        </is>
+      </c>
+      <c r="D79" s="37" t="inlineStr">
+        <is>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="F79" s="20" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="G79" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H79" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="20" t="inlineStr">
+        <is>
+          <t>Jul 21, 2026</t>
+        </is>
+      </c>
+      <c r="J79" s="20" t="inlineStr">
+        <is>
+          <t>26d</t>
+        </is>
+      </c>
+      <c r="K79" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L79" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
           <t>127EAX26Q0051</t>
         </is>
       </c>
-      <c r="D79" s="37" t="inlineStr">
+      <c r="D80" s="40" t="inlineStr">
         <is>
           <t>GAOA Accessible Upgrades Toilet Replacement</t>
         </is>
       </c>
-      <c r="E79" s="20" t="inlineStr">
+      <c r="E80" s="17" t="inlineStr">
         <is>
           <t>Sonora, California</t>
         </is>
       </c>
-      <c r="F79" s="20" t="inlineStr">
+      <c r="F80" s="17" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="G79" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H79" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="20" t="inlineStr">
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
         <is>
           <t>Jul 22, 2026</t>
         </is>
       </c>
-      <c r="J79" s="20" t="inlineStr">
+      <c r="J80" s="17" t="inlineStr">
         <is>
           <t>27d</t>
         </is>
       </c>
-      <c r="K79" s="43" t="inlineStr">
+      <c r="K80" s="43" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L79" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="39" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="B80" s="33" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="C80" s="23" t="inlineStr">
-        <is>
-          <t>36C25626R0015</t>
-        </is>
-      </c>
-      <c r="D80" s="28" t="inlineStr">
-        <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
-        </is>
-      </c>
-      <c r="E80" s="23" t="inlineStr">
-        <is>
-          <t>Fayetteville, Arkansas</t>
-        </is>
-      </c>
-      <c r="F80" s="23" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="G80" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H80" s="23" t="inlineStr">
-        <is>
-          <t>$15.0M</t>
-        </is>
-      </c>
-      <c r="I80" s="23" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="J80" s="23" t="inlineStr">
-        <is>
-          <t>28d</t>
-        </is>
-      </c>
-      <c r="K80" s="43" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L80" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="36" t="inlineStr">
+      <c r="L80" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -6441,22 +6441,22 @@
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
-          <t>W912P926R8225</t>
+          <t>15B41226Q00000006</t>
         </is>
       </c>
       <c r="D81" s="37" t="inlineStr">
         <is>
-          <t>Harlow Island Stage 1B</t>
+          <t>FMC Rochester Install Above Ground Tanks</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Rochester, Minnesota</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237120</t>
         </is>
       </c>
       <c r="G81" s="20" t="inlineStr">
@@ -6466,102 +6466,102 @@
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$375K</t>
         </is>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
+          <t>Jul 22, 2026</t>
+        </is>
+      </c>
+      <c r="J81" s="20" t="inlineStr">
+        <is>
+          <t>27d</t>
+        </is>
+      </c>
+      <c r="K81" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
+        </is>
+      </c>
+      <c r="L81" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="B82" s="33" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="C82" s="23" t="inlineStr">
+        <is>
+          <t>36C25626R0015</t>
+        </is>
+      </c>
+      <c r="D82" s="28" t="inlineStr">
+        <is>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+        </is>
+      </c>
+      <c r="E82" s="23" t="inlineStr">
+        <is>
+          <t>Fayetteville, Arkansas</t>
+        </is>
+      </c>
+      <c r="F82" s="23" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="G82" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H82" s="23" t="inlineStr">
+        <is>
+          <t>$15.0M</t>
+        </is>
+      </c>
+      <c r="I82" s="23" t="inlineStr">
+        <is>
           <t>Jul 23, 2026</t>
         </is>
       </c>
-      <c r="J81" s="20" t="inlineStr">
+      <c r="J82" s="23" t="inlineStr">
         <is>
           <t>28d</t>
         </is>
       </c>
-      <c r="K81" s="43" t="inlineStr">
+      <c r="K82" s="43" t="inlineStr">
         <is>
           <t>🟡 Soon</t>
         </is>
       </c>
-      <c r="L81" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="39" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="C82" s="17" t="inlineStr">
-        <is>
-          <t>W912P426BA002</t>
-        </is>
-      </c>
-      <c r="D82" s="40" t="inlineStr">
-        <is>
-          <t>Toledo Harbor/River Dredging</t>
-        </is>
-      </c>
-      <c r="E82" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="F82" s="17" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="G82" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H82" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="17" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="J82" s="17" t="inlineStr">
-        <is>
-          <t>28d</t>
-        </is>
-      </c>
-      <c r="K82" s="43" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
-        </is>
-      </c>
-      <c r="L82" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="42" t="inlineStr">
+      <c r="L82" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -6575,12 +6575,12 @@
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>127EAX26R0006</t>
+          <t>W912P926R8225</t>
         </is>
       </c>
       <c r="D83" s="37" t="inlineStr">
         <is>
-          <t>R3 National Forest’s Roads IDIQ</t>
+          <t>Harlow Island Stage 1B</t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="F83" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G83" s="20" t="inlineStr">
@@ -6600,17 +6600,17 @@
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>$72.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 23, 2026</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="K83" s="43" t="inlineStr">
@@ -6642,12 +6642,12 @@
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>W50S7X26BA003</t>
+          <t>W912P426BA002</t>
         </is>
       </c>
       <c r="D84" s="40" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>Toledo Harbor/River Dredging</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="G84" s="17" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 23, 2026</t>
         </is>
       </c>
       <c r="J84" s="17" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="K84" s="43" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
-          <t>140FGA26R0024</t>
+          <t>127EAX26R0006</t>
         </is>
       </c>
       <c r="D85" s="37" t="inlineStr">
         <is>
-          <t>EO</t>
+          <t>R3 National Forest’s Roads IDIQ</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
@@ -6734,22 +6734,22 @@
       </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$72.5M</t>
         </is>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
-          <t>32d</t>
-        </is>
-      </c>
-      <c r="K85" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="K85" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L85" s="20" t="inlineStr">
@@ -6776,17 +6776,17 @@
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>SV0218-26</t>
+          <t>W50S7X26BA003</t>
         </is>
       </c>
       <c r="D86" s="40" t="inlineStr">
         <is>
-          <t>Electrical Infrastructure Upgrade (Optics)</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>Butner, North Carolina</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
@@ -6806,17 +6806,17 @@
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
-          <t>Aug 05, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="J86" s="17" t="inlineStr">
         <is>
-          <t>41d</t>
-        </is>
-      </c>
-      <c r="K86" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+          <t>29d</t>
+        </is>
+      </c>
+      <c r="K86" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="L86" s="17" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="C87" s="20" t="inlineStr">
         <is>
-          <t>140P6426Q0073</t>
+          <t>140FGA26R0024</t>
         </is>
       </c>
       <c r="D87" s="37" t="inlineStr">
         <is>
-          <t>Crack and Fog Sealing Multiple Locations</t>
+          <t>EO</t>
         </is>
       </c>
       <c r="E87" s="20" t="inlineStr">
@@ -6868,22 +6868,22 @@
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jul 27, 2026</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K87" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+          <t>32d</t>
+        </is>
+      </c>
+      <c r="K87" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="L87" s="20" t="inlineStr">
@@ -6910,127 +6910,127 @@
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>W50S9526BA002</t>
+          <t>SV0218-26</t>
         </is>
       </c>
       <c r="D88" s="40" t="inlineStr">
         <is>
-          <t>Repair and Widen Taxiways Phase III, PSTE 162013</t>
+          <t>Electrical Infrastructure Upgrade (Optics)</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
+          <t>Butner, North Carolina</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>Aug 05, 2026</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>41d</t>
+        </is>
+      </c>
+      <c r="K88" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
+        </is>
+      </c>
+      <c r="L88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M88" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N88" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="C89" s="20" t="inlineStr">
+        <is>
+          <t>140P6426Q0073</t>
+        </is>
+      </c>
+      <c r="D89" s="37" t="inlineStr">
+        <is>
+          <t>Crack and Fog Sealing Multiple Locations</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
+        <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="F88" s="17" t="inlineStr">
+      <c r="F89" s="20" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="G88" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H88" s="17" t="inlineStr">
-        <is>
-          <t>$22.5M</t>
-        </is>
-      </c>
-      <c r="I88" s="17" t="inlineStr">
+      <c r="G89" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H89" s="20" t="inlineStr">
+        <is>
+          <t>$45.0M</t>
+        </is>
+      </c>
+      <c r="I89" s="20" t="inlineStr">
         <is>
           <t>Jun 25, 2026</t>
         </is>
       </c>
-      <c r="J88" s="17" t="inlineStr">
+      <c r="J89" s="20" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="K88" s="18" t="inlineStr">
+      <c r="K89" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L88" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M88" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N88" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="32" customHeight="1">
-      <c r="B89" s="33" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C89" s="23" t="inlineStr">
-        <is>
-          <t>W9128F26RA063</t>
-        </is>
-      </c>
-      <c r="D89" s="28" t="inlineStr">
-        <is>
-          <t>Fort Riley Tank CoatingsRepair</t>
-        </is>
-      </c>
-      <c r="E89" s="23" t="inlineStr">
-        <is>
-          <t>Fort Riley, Kansas</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr">
-        <is>
-          <t>237120</t>
-        </is>
-      </c>
-      <c r="G89" s="34" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I89" s="23" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="J89" s="23" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="K89" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
-        </is>
-      </c>
-      <c r="L89" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M89" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N89" s="36" t="inlineStr">
+      <c r="L89" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M89" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>W911KB26RA039</t>
+          <t>W50S9526BA002</t>
         </is>
       </c>
       <c r="D90" s="40" t="inlineStr">
         <is>
-          <t>FTW506 Life Safety Repairs</t>
+          <t>Repair and Widen Taxiways Phase III, PSTE 162013</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="G90" s="17" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="H90" s="17" t="inlineStr">
         <is>
-          <t>$18.0M</t>
+          <t>$22.5M</t>
         </is>
       </c>
       <c r="I90" s="17" t="inlineStr">
@@ -7104,47 +7104,47 @@
       </c>
     </row>
     <row r="91" ht="32" customHeight="1">
-      <c r="B91" s="20" t="inlineStr">
+      <c r="B91" s="33" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="C91" s="20" t="inlineStr">
-        <is>
-          <t>1605AE-26-Q-00005</t>
-        </is>
-      </c>
-      <c r="D91" s="37" t="inlineStr">
-        <is>
-          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
-        </is>
-      </c>
-      <c r="E91" s="20" t="inlineStr">
-        <is>
-          <t>Atlanta, Georgia</t>
-        </is>
-      </c>
-      <c r="F91" s="20" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="G91" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="H91" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I91" s="20" t="inlineStr">
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>W9128F26RA063</t>
+        </is>
+      </c>
+      <c r="D91" s="28" t="inlineStr">
+        <is>
+          <t>Fort Riley Tank CoatingsRepair</t>
+        </is>
+      </c>
+      <c r="E91" s="23" t="inlineStr">
+        <is>
+          <t>Fort Riley, Kansas</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>237120</t>
+        </is>
+      </c>
+      <c r="G91" s="34" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="H91" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="23" t="inlineStr">
         <is>
           <t>Jun 25, 2026</t>
         </is>
       </c>
-      <c r="J91" s="20" t="inlineStr">
+      <c r="J91" s="23" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
@@ -7154,17 +7154,17 @@
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="L91" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M91" s="38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N91" s="39" t="inlineStr">
+      <c r="L91" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M91" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -7178,17 +7178,17 @@
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>FA469026Q0030</t>
+          <t>W911KB26RA039</t>
         </is>
       </c>
       <c r="D92" s="40" t="inlineStr">
         <is>
-          <t>Video Intercom System</t>
+          <t>FTW506 Life Safety Repairs</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>Ellsworth AFB, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$18.0M</t>
         </is>
       </c>
       <c r="I92" s="17" t="inlineStr">
@@ -7237,8 +7237,75 @@
         </is>
       </c>
     </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="inlineStr">
+        <is>
+          <t>1605AE-26-Q-00005</t>
+        </is>
+      </c>
+      <c r="D93" s="37" t="inlineStr">
+        <is>
+          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="20" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026</t>
+        </is>
+      </c>
+      <c r="J93" s="20" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="K93" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
+        </is>
+      </c>
+      <c r="L93" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M93" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B5:N92"/>
+  <autoFilter ref="B5:N93"/>
   <mergeCells count="2">
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B2:N2"/>
@@ -7331,6 +7398,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N90" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N91" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N92" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N93" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7343,7 +7411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K42"/>
+  <dimension ref="B2:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7371,7 +7439,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Early-stage opportunities to monitor  ·  37 records  (7 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
+          <t>Early-stage opportunities to monitor  ·  38 records  (7 SDVOSB)  ·  SDVOSB first, then AI score desc</t>
         </is>
       </c>
     </row>
@@ -7899,22 +7967,22 @@
     <row r="15" ht="32" customHeight="1">
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
+          <t>1305M4-26-R-0034</t>
         </is>
       </c>
       <c r="C15" s="37" t="inlineStr">
         <is>
-          <t>Repair Hush House Concrete B3857</t>
+          <t>Design-Build Repair and Renovation of the Gulf Marine Service Facility (GMSF) &amp; Wharf Repairs, in Pascagoula, Mississippi</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Pascagoula, Mississippi</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -7924,17 +7992,17 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>$23.0M</t>
+          <t>$23.5M</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -7951,12 +8019,12 @@
     <row r="16" ht="32" customHeight="1">
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>140L3726R0006</t>
+          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
         </is>
       </c>
       <c r="C16" s="40" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>Repair Hush House Concrete B3857</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -7966,7 +8034,7 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -7976,17 +8044,17 @@
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>$23.0M</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>64d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J16" s="17" t="inlineStr">
@@ -8003,12 +8071,12 @@
     <row r="17" ht="32" customHeight="1">
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>140FGA26R0028</t>
+          <t>140L3726R0006</t>
         </is>
       </c>
       <c r="C17" s="37" t="inlineStr">
         <is>
-          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -8018,7 +8086,7 @@
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -8028,17 +8096,17 @@
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>64d</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -8055,22 +8123,22 @@
     <row r="18" ht="32" customHeight="1">
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>140R6026R0016</t>
+          <t>140FGA26R0028</t>
         </is>
       </c>
       <c r="C18" s="40" t="inlineStr">
         <is>
-          <t>Z--Webster Dam, Spillway Radial Gates Repair, Webster Unit, Solomon Division, Pick</t>
+          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
@@ -8080,22 +8148,22 @@
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>$7.5M</t>
+          <t>$11.8M</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>Aug 10, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
-          <t>46d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -8107,22 +8175,22 @@
     <row r="19" ht="32" customHeight="1">
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>W9123826RA018</t>
+          <t>140R6026R0016</t>
         </is>
       </c>
       <c r="C19" s="37" t="inlineStr">
         <is>
-          <t>USACE SPK DB Construction – DDJC Centralized Gas and Electric Metering - Tracy, CA</t>
+          <t>Z--Webster Dam, Spillway Radial Gates Repair, Webster Unit, Solomon Division, Pick</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>Tracy, California</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -8137,17 +8205,17 @@
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Aug 10, 2026</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>46d</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -8159,22 +8227,22 @@
     <row r="20" ht="32" customHeight="1">
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>W9133L26BA010</t>
+          <t>W9123826RA018</t>
         </is>
       </c>
       <c r="C20" s="40" t="inlineStr">
         <is>
-          <t>Air National Guard (ANG) Smart Meters</t>
+          <t>USACE SPK DB Construction – DDJC Centralized Gas and Electric Metering - Tracy, CA</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tracy, California</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -8184,17 +8252,17 @@
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>$4.2M</t>
+          <t>$7.5M</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J20" s="17" t="inlineStr">
@@ -8211,12 +8279,12 @@
     <row r="21" ht="32" customHeight="1">
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>PANNWD26P0000028054</t>
+          <t>W9133L26BA010</t>
         </is>
       </c>
       <c r="C21" s="37" t="inlineStr">
         <is>
-          <t>Levee Repair at MRLS L246</t>
+          <t>Air National Guard (ANG) Smart Meters</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -8226,7 +8294,7 @@
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -8236,17 +8304,17 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>$4.2M</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -8263,12 +8331,12 @@
     <row r="22" ht="32" customHeight="1">
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>W912DR26BA007</t>
+          <t>PANNWD26P0000028054</t>
         </is>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
+          <t>Levee Repair at MRLS L246</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
@@ -8293,12 +8361,12 @@
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J22" s="17" t="inlineStr">
@@ -8315,22 +8383,22 @@
     <row r="23" ht="32" customHeight="1">
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>75H70126R00029</t>
+          <t>W912DR26BA007</t>
         </is>
       </c>
       <c r="C23" s="37" t="inlineStr">
         <is>
-          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
+          <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>Pine Ridge, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -8345,12 +8413,12 @@
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>Jul 31, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -8367,22 +8435,22 @@
     <row r="24" ht="32" customHeight="1">
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>693C73-26-B-000017</t>
+          <t>75H70126R00029</t>
         </is>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>Project VI NP VIIS 100(3) - Rehabilitation of Lameshur Road  in St. John, U.S. Virgin Islands</t>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Pine Ridge, South Dakota</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -8392,17 +8460,17 @@
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>$2.5M</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>Aug 04, 2026</t>
+          <t>Jul 31, 2026</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>40d</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="J24" s="17" t="inlineStr">
@@ -8419,22 +8487,22 @@
     <row r="25" ht="32" customHeight="1">
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>140FGA26R0023</t>
+          <t>693C73-26-B-000017</t>
         </is>
       </c>
       <c r="C25" s="37" t="inlineStr">
         <is>
-          <t>Y--Boat Ramp Replacement Project at Kirwin NWR</t>
+          <t>Project VI NP VIIS 100(3) - Rehabilitation of Lameshur Road  in St. John, U.S. Virgin Islands</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>Kirwin, Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -8444,17 +8512,17 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>$2.5M</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
-          <t>Jul 31, 2026</t>
+          <t>Aug 04, 2026</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>40d</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -8471,22 +8539,22 @@
     <row r="26" ht="32" customHeight="1">
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>W912WJ26QA124</t>
+          <t>140FGA26R0023</t>
         </is>
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
-          <t>Road Gate Painting, Road Gate Installation, Removal and Replacement of Guardrails, Buffumville Lake, Charlton, MA</t>
+          <t>Y--Boat Ramp Replacement Project at Kirwin NWR</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Kirwin, Kansas</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -8496,17 +8564,17 @@
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>$175K</t>
+          <t>$750K</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jul 31, 2026</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="J26" s="17" t="inlineStr">
@@ -8523,17 +8591,17 @@
     <row r="27" ht="32" customHeight="1">
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>W9127826RA025</t>
+          <t>W912WJ26QA124</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
         <is>
-          <t>Phillips Parkway Haul Route</t>
+          <t>Road Gate Painting, Road Gate Installation, Removal and Replacement of Guardrails, Buffumville Lake, Charlton, MA</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>Cape Canaveral, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -8548,7 +8616,7 @@
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$175K</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -8563,7 +8631,7 @@
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
@@ -8575,22 +8643,22 @@
     <row r="28" ht="32" customHeight="1">
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>140P5326R0019</t>
+          <t>W9127826RA025</t>
         </is>
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>Phillips Parkway Haul Route</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Cape Canaveral, Florida</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -8615,7 +8683,7 @@
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="K28" s="17" t="inlineStr">
@@ -8627,12 +8695,12 @@
     <row r="29" ht="32" customHeight="1">
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>SP470525R002026</t>
+          <t>140P5326R0019</t>
         </is>
       </c>
       <c r="C29" s="37" t="inlineStr">
         <is>
-          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -8642,7 +8710,7 @@
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -8657,17 +8725,17 @@
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -8679,12 +8747,12 @@
     <row r="30" ht="32" customHeight="1">
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>W912HY26BA030</t>
+          <t>SP470525R002026</t>
         </is>
       </c>
       <c r="C30" s="40" t="inlineStr">
         <is>
-          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
+          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
@@ -8694,7 +8762,7 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -8709,17 +8777,17 @@
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Special Notice</t>
         </is>
       </c>
       <c r="K30" s="17" t="inlineStr">
@@ -8731,12 +8799,12 @@
     <row r="31" ht="32" customHeight="1">
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>W912HY26BA030</t>
         </is>
       </c>
       <c r="C31" s="37" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -8746,7 +8814,7 @@
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -8761,12 +8829,12 @@
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -8783,12 +8851,12 @@
     <row r="32" ht="32" customHeight="1">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C32" s="40" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
@@ -8798,7 +8866,7 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
@@ -8835,22 +8903,22 @@
     <row r="33" ht="32" customHeight="1">
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>W912EE26RA015</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C33" s="37" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -8865,12 +8933,12 @@
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -8887,22 +8955,22 @@
     <row r="34" ht="32" customHeight="1">
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C34" s="40" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -8917,12 +8985,12 @@
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="J34" s="17" t="inlineStr">
@@ -8939,12 +9007,12 @@
     <row r="35" ht="32" customHeight="1">
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C35" s="37" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -8954,7 +9022,7 @@
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -8991,12 +9059,12 @@
     <row r="36" ht="32" customHeight="1">
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0017</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C36" s="40" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
@@ -9006,7 +9074,7 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
@@ -9043,22 +9111,22 @@
     <row r="37" ht="32" customHeight="1">
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>140P6326B0008</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C37" s="37" t="inlineStr">
         <is>
-          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>Medora, North Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
@@ -9073,12 +9141,12 @@
       </c>
       <c r="H37" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J37" s="20" t="inlineStr">
@@ -9095,17 +9163,17 @@
     <row r="38" ht="32" customHeight="1">
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>140P8526Q0083</t>
+          <t>140P6326B0008</t>
         </is>
       </c>
       <c r="C38" s="40" t="inlineStr">
         <is>
-          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Medora, North Dakota</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
@@ -9125,12 +9193,12 @@
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J38" s="17" t="inlineStr">
@@ -9147,12 +9215,12 @@
     <row r="39" ht="32" customHeight="1">
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>140P9726Q0046</t>
+          <t>140P8526Q0083</t>
         </is>
       </c>
       <c r="C39" s="37" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -9162,7 +9230,7 @@
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -9199,22 +9267,22 @@
     <row r="40" ht="32" customHeight="1">
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>W50S85-26-B-A007</t>
+          <t>140P9726Q0046</t>
         </is>
       </c>
       <c r="C40" s="40" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
@@ -9229,12 +9297,12 @@
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J40" s="17" t="inlineStr">
@@ -9251,22 +9319,22 @@
     <row r="41" ht="32" customHeight="1">
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>W912DQ26QA063</t>
+          <t>W50S85-26-B-A007</t>
         </is>
       </c>
       <c r="C41" s="37" t="inlineStr">
         <is>
-          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+          <t>Feeder #7 Repair</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Stockton, Missouri</t>
+          <t>Selfridge ANGB, Michigan</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -9281,12 +9349,12 @@
       </c>
       <c r="H41" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="I41" s="20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="J41" s="20" t="inlineStr">
@@ -9303,57 +9371,109 @@
     <row r="42" ht="32" customHeight="1">
       <c r="B42" s="17" t="inlineStr">
         <is>
+          <t>W912DQ26QA063</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>Stockton, Missouri</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="B43" s="20" t="inlineStr">
+        <is>
           <t>140R4025R0017</t>
         </is>
       </c>
-      <c r="C42" s="40" t="inlineStr">
+      <c r="C43" s="37" t="inlineStr">
         <is>
           <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E43" s="20" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="17" t="inlineStr">
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
         <is>
           <t>Jul 16, 2026</t>
         </is>
       </c>
-      <c r="I42" s="17" t="inlineStr">
+      <c r="I43" s="20" t="inlineStr">
         <is>
           <t>21d</t>
         </is>
       </c>
-      <c r="J42" s="17" t="inlineStr">
+      <c r="J43" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K42" s="17" t="inlineStr">
+      <c r="K43" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K42"/>
+  <autoFilter ref="B5:K43"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -9369,7 +9489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K129"/>
+  <dimension ref="B2:K131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -9397,7 +9517,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>Complete data  ·  124 records  ·  June 24, 2026</t>
+          <t>Complete data  ·  126 records  ·  June 24, 2026</t>
         </is>
       </c>
     </row>
@@ -10289,22 +10409,22 @@
     <row r="22" ht="28" customHeight="1">
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>W911WN26BA014</t>
+          <t>12FPC326B0006</t>
         </is>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Madison, Ohio</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -10314,7 +10434,7 @@
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
@@ -10341,22 +10461,22 @@
     <row r="23" ht="28" customHeight="1">
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>12FPC326B0006</t>
+          <t>FA481426Q0026</t>
         </is>
       </c>
       <c r="C23" s="37" t="inlineStr">
         <is>
-          <t>ACEP WRE Easement Repair (Dike Repair)-Madison Township, Perry County, Ohio</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>Madison, Ohio</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -10393,17 +10513,17 @@
     <row r="24" ht="28" customHeight="1">
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>FA481426Q0026</t>
+          <t>W912ES26QA067</t>
         </is>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Fiber Optic Cable Replacement</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
@@ -10443,52 +10563,52 @@
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>W912ES26QA067</t>
-        </is>
-      </c>
-      <c r="C25" s="37" t="inlineStr">
-        <is>
-          <t>Fiber Optic Cable Replacement</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>36C25226Q0526</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>Madison, Wisconsin</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="J25" s="20" t="inlineStr">
+      <c r="J25" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K25" s="39" t="inlineStr">
+      <c r="K25" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -10497,22 +10617,22 @@
     <row r="26" ht="28" customHeight="1">
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>36C25226Q0526</t>
+          <t>36C78626B0007</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>Fiber Optic Cable and installation - Paging System Upgrade and Expansion</t>
+          <t>Y1PZ--810CM3033 Gravesite Expansion with FCA Deficiencies at  Dayton National Cemetery</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>Madison, Wisconsin</t>
+          <t>Dayton, Ohio</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
@@ -10547,52 +10667,52 @@
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>36C78626B0007</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="inlineStr">
-        <is>
-          <t>Y1PZ--810CM3033 Gravesite Expansion with FCA Deficiencies at  Dayton National Cemetery</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
-        <is>
-          <t>Dayton, Ohio</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="23" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="I27" s="23" t="inlineStr">
-        <is>
-          <t>5d</t>
-        </is>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>140P9726R0002</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>Y--GLBA REHAB WATERLINE</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>Jul 01, 2026</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>6d</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K27" s="36" t="inlineStr">
+      <c r="K27" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -10601,12 +10721,12 @@
     <row r="28" ht="28" customHeight="1">
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>140P9726R0002</t>
+          <t>140A1626QD002</t>
         </is>
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>Y--GLBA REHAB WATERLINE</t>
+          <t>N-- AIRR Security Cameras &amp; Badging for BTFA</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
@@ -10616,7 +10736,7 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -10653,12 +10773,12 @@
     <row r="29" ht="28" customHeight="1">
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>140A1626QD002</t>
+          <t>140P6426B0004</t>
         </is>
       </c>
       <c r="C29" s="37" t="inlineStr">
         <is>
-          <t>N-- AIRR Security Cameras &amp; Badging for BTFA</t>
+          <t>Z--Munising Falls Trail Rehabilitation</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -10668,7 +10788,7 @@
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -10705,22 +10825,22 @@
     <row r="30" ht="28" customHeight="1">
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>140P6426B0004</t>
+          <t>140P6026B0004</t>
         </is>
       </c>
       <c r="C30" s="40" t="inlineStr">
         <is>
-          <t>Z--Munising Falls Trail Rehabilitation</t>
+          <t>Z--BRVB - Entry Courtyard Improvements</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Topeka, Kansas</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -10735,12 +10855,12 @@
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>Jul 01, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="J30" s="17" t="inlineStr">
@@ -10757,22 +10877,22 @@
     <row r="31" ht="28" customHeight="1">
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>140P6026B0004</t>
+          <t>140P8326Q0042</t>
         </is>
       </c>
       <c r="C31" s="37" t="inlineStr">
         <is>
-          <t>Z--BRVB - Entry Courtyard Improvements</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>Topeka, Kansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -10782,7 +10902,7 @@
       </c>
       <c r="G31" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -10809,12 +10929,12 @@
     <row r="32" ht="28" customHeight="1">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>140P8326Q0042</t>
+          <t>1305M326Q0251</t>
         </is>
       </c>
       <c r="C32" s="40" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>NOAA Western Regional Center H32 Electrical Repair</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
@@ -10824,7 +10944,7 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
@@ -10834,7 +10954,7 @@
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
@@ -10861,12 +10981,12 @@
     <row r="33" ht="28" customHeight="1">
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>1305M326Q0251</t>
+          <t>140FC226Q0036</t>
         </is>
       </c>
       <c r="C33" s="37" t="inlineStr">
         <is>
-          <t>NOAA Western Regional Center H32 Electrical Repair</t>
+          <t>VY-MISSISQUOI NWR-PARKING LOT MAINT</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -10876,7 +10996,7 @@
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -10886,17 +11006,17 @@
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jul 03, 2026</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -10913,22 +11033,22 @@
     <row r="34" ht="28" customHeight="1">
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>140FC226Q0036</t>
+          <t>FA469026Q0030</t>
         </is>
       </c>
       <c r="C34" s="40" t="inlineStr">
         <is>
-          <t>VY-MISSISQUOI NWR-PARKING LOT MAINT</t>
+          <t>Video Intercom System</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Ellsworth AFB, South Dakota</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
@@ -12629,12 +12749,12 @@
     <row r="67" ht="28" customHeight="1">
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>89503426BWA000068</t>
+          <t>W911WN26BA014</t>
         </is>
       </c>
       <c r="C67" s="37" t="inlineStr">
         <is>
-          <t>Beresford Substation Stage 11, South Dakota</t>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -12644,7 +12764,7 @@
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
@@ -12654,17 +12774,17 @@
       </c>
       <c r="G67" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 14, 2026</t>
         </is>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="J67" s="20" t="inlineStr">
@@ -12681,12 +12801,12 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>140L3626Q0032</t>
+          <t>89503426BWA000068</t>
         </is>
       </c>
       <c r="C68" s="40" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -12696,7 +12816,7 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
@@ -12733,22 +12853,22 @@
     <row r="69" ht="28" customHeight="1">
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>75F40126R00051</t>
+          <t>140L3626Q0032</t>
         </is>
       </c>
       <c r="C69" s="37" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>561210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
@@ -12785,22 +12905,22 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>140P2026R0011</t>
+          <t>75F40126R00051</t>
         </is>
       </c>
       <c r="C70" s="40" t="inlineStr">
         <is>
-          <t>GLCA Hite</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
@@ -12837,12 +12957,12 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>W9127826RA059</t>
+          <t>140P2026R0011</t>
         </is>
       </c>
       <c r="C71" s="37" t="inlineStr">
         <is>
-          <t>Water Tank Storage</t>
+          <t>GLCA Hite</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
@@ -12852,7 +12972,7 @@
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
@@ -12867,12 +12987,12 @@
       </c>
       <c r="H71" s="20" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
@@ -12889,154 +13009,154 @@
     <row r="72" ht="28" customHeight="1">
       <c r="B72" s="17" t="inlineStr">
         <is>
+          <t>W9127826RA059</t>
+        </is>
+      </c>
+      <c r="C72" s="40" t="inlineStr">
+        <is>
+          <t>Water Tank Storage</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>Jul 16, 2026</t>
+        </is>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>21d</t>
+        </is>
+      </c>
+      <c r="J72" s="17" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K72" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="B73" s="20" t="inlineStr">
+        <is>
           <t>W912HN26BA008</t>
         </is>
       </c>
-      <c r="C72" s="40" t="inlineStr">
+      <c r="C73" s="37" t="inlineStr">
         <is>
           <t>FY26 Brunswick Inner Harbor Dredging Project</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="D73" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E72" s="17" t="inlineStr">
+      <c r="E73" s="20" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="F72" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G72" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="17" t="inlineStr">
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
         <is>
           <t>Jul 17, 2026</t>
         </is>
       </c>
-      <c r="I72" s="17" t="inlineStr">
+      <c r="I73" s="20" t="inlineStr">
         <is>
           <t>22d</t>
         </is>
       </c>
-      <c r="J72" s="17" t="inlineStr">
+      <c r="J73" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K72" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="28" customHeight="1">
-      <c r="B73" s="23" t="inlineStr">
+      <c r="K73" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="B74" s="23" t="inlineStr">
         <is>
           <t>W50S6T26QA026</t>
         </is>
       </c>
-      <c r="C73" s="28" t="inlineStr">
+      <c r="C74" s="28" t="inlineStr">
         <is>
           <t>Remove Traffic Island and Construct Sloped Concrete Static Display</t>
         </is>
       </c>
-      <c r="D73" s="23" t="inlineStr">
+      <c r="D74" s="23" t="inlineStr">
         <is>
           <t>California</t>
         </is>
       </c>
-      <c r="E73" s="23" t="inlineStr">
+      <c r="E74" s="23" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F73" s="23" t="inlineStr">
+      <c r="F74" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G73" s="23" t="inlineStr">
+      <c r="G74" s="23" t="inlineStr">
         <is>
           <t>$25K</t>
         </is>
       </c>
-      <c r="H73" s="23" t="inlineStr">
+      <c r="H74" s="23" t="inlineStr">
         <is>
           <t>Jul 17, 2026</t>
         </is>
       </c>
-      <c r="I73" s="23" t="inlineStr">
+      <c r="I74" s="23" t="inlineStr">
         <is>
           <t>22d</t>
         </is>
       </c>
-      <c r="J73" s="23" t="inlineStr">
+      <c r="J74" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K73" s="36" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>FA301626B0001</t>
-        </is>
-      </c>
-      <c r="C74" s="40" t="inlineStr">
-        <is>
-          <t>Repair Carswell Ave.</t>
-        </is>
-      </c>
-      <c r="D74" s="17" t="inlineStr">
-        <is>
-          <t>DWG, Texas</t>
-        </is>
-      </c>
-      <c r="E74" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F74" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G74" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="17" t="inlineStr">
-        <is>
-          <t>Jul 17, 2026</t>
-        </is>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>22d</t>
-        </is>
-      </c>
-      <c r="J74" s="17" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K74" s="42" t="inlineStr">
+      <c r="K74" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13045,22 +13165,22 @@
     <row r="75" ht="28" customHeight="1">
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>140P8326Q0046</t>
+          <t>FA301626B0001</t>
         </is>
       </c>
       <c r="C75" s="37" t="inlineStr">
         <is>
-          <t>LARO-DRILL NEW WATER WELL - SHERMAN HOMES CABINS</t>
+          <t>Repair Carswell Ave.</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>DWG, Texas</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
@@ -13097,17 +13217,17 @@
     <row r="76" ht="28" customHeight="1">
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>75H70126R00030</t>
+          <t>140P8326Q0046</t>
         </is>
       </c>
       <c r="C76" s="40" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>LARO-DRILL NEW WATER WELL - SHERMAN HOMES CABINS</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -13122,17 +13242,17 @@
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>Jul 20, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="J76" s="17" t="inlineStr">
@@ -13149,22 +13269,22 @@
     <row r="77" ht="28" customHeight="1">
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>693C73-26-R-000047</t>
+          <t>75H70126R00030</t>
         </is>
       </c>
       <c r="C77" s="37" t="inlineStr">
         <is>
-          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
+          <t>Rosebud Lift Station Construction</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Rosebud, South Dakota</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
@@ -13174,17 +13294,17 @@
       </c>
       <c r="G77" s="20" t="inlineStr">
         <is>
-          <t>$12.9M</t>
+          <t>$11.8M</t>
         </is>
       </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
-          <t>Jul 21, 2026</t>
+          <t>Jul 20, 2026</t>
         </is>
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>26d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="J77" s="20" t="inlineStr">
@@ -13201,12 +13321,12 @@
     <row r="78" ht="28" customHeight="1">
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>W912ES26BA013</t>
+          <t>693C73-26-R-000047</t>
         </is>
       </c>
       <c r="C78" s="40" t="inlineStr">
         <is>
-          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+          <t>Northeast Region Construction Multiple Award Task Order Contract (MATOC)</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
@@ -13216,7 +13336,7 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
@@ -13226,7 +13346,7 @@
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$12.9M</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
@@ -13253,102 +13373,102 @@
     <row r="79" ht="28" customHeight="1">
       <c r="B79" s="20" t="inlineStr">
         <is>
+          <t>W912ES26BA013</t>
+        </is>
+      </c>
+      <c r="C79" s="37" t="inlineStr">
+        <is>
+          <t>RENO BOTTOMS HREP - STAGE 2 - ICE HAUL SLOUGH</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F79" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G79" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="20" t="inlineStr">
+        <is>
+          <t>Jul 21, 2026</t>
+        </is>
+      </c>
+      <c r="I79" s="20" t="inlineStr">
+        <is>
+          <t>26d</t>
+        </is>
+      </c>
+      <c r="J79" s="20" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K79" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="B80" s="17" t="inlineStr">
+        <is>
           <t>127EAX26Q0051</t>
         </is>
       </c>
-      <c r="C79" s="37" t="inlineStr">
+      <c r="C80" s="40" t="inlineStr">
         <is>
           <t>GAOA Accessible Upgrades Toilet Replacement</t>
         </is>
       </c>
-      <c r="D79" s="20" t="inlineStr">
+      <c r="D80" s="17" t="inlineStr">
         <is>
           <t>Sonora, California</t>
         </is>
       </c>
-      <c r="E79" s="20" t="inlineStr">
+      <c r="E80" s="17" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="F79" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G79" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="20" t="inlineStr">
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
         <is>
           <t>Jul 22, 2026</t>
         </is>
       </c>
-      <c r="I79" s="20" t="inlineStr">
+      <c r="I80" s="17" t="inlineStr">
         <is>
           <t>27d</t>
         </is>
       </c>
-      <c r="J79" s="20" t="inlineStr">
+      <c r="J80" s="17" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K79" s="39" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="B80" s="23" t="inlineStr">
-        <is>
-          <t>36C25626R0015</t>
-        </is>
-      </c>
-      <c r="C80" s="28" t="inlineStr">
-        <is>
-          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
-        </is>
-      </c>
-      <c r="D80" s="23" t="inlineStr">
-        <is>
-          <t>Fayetteville, Arkansas</t>
-        </is>
-      </c>
-      <c r="E80" s="23" t="inlineStr">
-        <is>
-          <t>237110</t>
-        </is>
-      </c>
-      <c r="F80" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="inlineStr">
-        <is>
-          <t>$15.0M</t>
-        </is>
-      </c>
-      <c r="H80" s="23" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="I80" s="23" t="inlineStr">
-        <is>
-          <t>28d</t>
-        </is>
-      </c>
-      <c r="J80" s="23" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K80" s="36" t="inlineStr">
+      <c r="K80" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13357,22 +13477,22 @@
     <row r="81" ht="28" customHeight="1">
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>W912P926R8225</t>
+          <t>15B41226Q00000006</t>
         </is>
       </c>
       <c r="C81" s="37" t="inlineStr">
         <is>
-          <t>Harlow Island Stage 1B</t>
+          <t>FMC Rochester Install Above Ground Tanks</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Rochester, Minnesota</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237120</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
@@ -13382,77 +13502,77 @@
       </c>
       <c r="G81" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$375K</t>
         </is>
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
+          <t>Jul 22, 2026</t>
+        </is>
+      </c>
+      <c r="I81" s="20" t="inlineStr">
+        <is>
+          <t>27d</t>
+        </is>
+      </c>
+      <c r="J81" s="20" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K81" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="B82" s="23" t="inlineStr">
+        <is>
+          <t>36C25626R0015</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>Y1NE| SOLICIATION | 36C25626R0015 | CONSTRUCT NEW WATER STORAGE FACILITY</t>
+        </is>
+      </c>
+      <c r="D82" s="23" t="inlineStr">
+        <is>
+          <t>Fayetteville, Arkansas</t>
+        </is>
+      </c>
+      <c r="E82" s="23" t="inlineStr">
+        <is>
+          <t>237110</t>
+        </is>
+      </c>
+      <c r="F82" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr">
+        <is>
+          <t>$15.0M</t>
+        </is>
+      </c>
+      <c r="H82" s="23" t="inlineStr">
+        <is>
           <t>Jul 23, 2026</t>
         </is>
       </c>
-      <c r="I81" s="20" t="inlineStr">
+      <c r="I82" s="23" t="inlineStr">
         <is>
           <t>28d</t>
         </is>
       </c>
-      <c r="J81" s="20" t="inlineStr">
+      <c r="J82" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K81" s="39" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>W912P426BA002</t>
-        </is>
-      </c>
-      <c r="C82" s="40" t="inlineStr">
-        <is>
-          <t>Toledo Harbor/River Dredging</t>
-        </is>
-      </c>
-      <c r="D82" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E82" s="17" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F82" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G82" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="17" t="inlineStr">
-        <is>
-          <t>Jul 23, 2026</t>
-        </is>
-      </c>
-      <c r="I82" s="17" t="inlineStr">
-        <is>
-          <t>28d</t>
-        </is>
-      </c>
-      <c r="J82" s="17" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K82" s="42" t="inlineStr">
+      <c r="K82" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13461,12 +13581,12 @@
     <row r="83" ht="28" customHeight="1">
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>127EAX26R0006</t>
+          <t>W912P926R8225</t>
         </is>
       </c>
       <c r="C83" s="37" t="inlineStr">
         <is>
-          <t>R3 National Forest’s Roads IDIQ</t>
+          <t>Harlow Island Stage 1B</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -13476,7 +13596,7 @@
       </c>
       <c r="E83" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
@@ -13486,17 +13606,17 @@
       </c>
       <c r="G83" s="20" t="inlineStr">
         <is>
-          <t>$72.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 23, 2026</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
@@ -13513,12 +13633,12 @@
     <row r="84" ht="28" customHeight="1">
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>W50S7X26BA003</t>
+          <t>W912P426BA002</t>
         </is>
       </c>
       <c r="C84" s="40" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>Toledo Harbor/River Dredging</t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
@@ -13528,7 +13648,7 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
@@ -13543,12 +13663,12 @@
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 23, 2026</t>
         </is>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>28d</t>
         </is>
       </c>
       <c r="J84" s="17" t="inlineStr">
@@ -13565,12 +13685,12 @@
     <row r="85" ht="28" customHeight="1">
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>140FGA26R0024</t>
+          <t>127EAX26R0006</t>
         </is>
       </c>
       <c r="C85" s="37" t="inlineStr">
         <is>
-          <t>EO</t>
+          <t>R3 National Forest’s Roads IDIQ</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
@@ -13590,17 +13710,17 @@
       </c>
       <c r="G85" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$72.5M</t>
         </is>
       </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>Jul 27, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>32d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
@@ -13617,17 +13737,17 @@
     <row r="86" ht="28" customHeight="1">
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>SV0218-26</t>
+          <t>W50S7X26BA003</t>
         </is>
       </c>
       <c r="C86" s="40" t="inlineStr">
         <is>
-          <t>Electrical Infrastructure Upgrade (Optics)</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t>Butner, North Carolina</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -13647,12 +13767,12 @@
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>Aug 05, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
-          <t>41d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J86" s="17" t="inlineStr">
@@ -13669,12 +13789,12 @@
     <row r="87" ht="28" customHeight="1">
       <c r="B87" s="20" t="inlineStr">
         <is>
-          <t>140P6426Q0073</t>
+          <t>140FGA26R0024</t>
         </is>
       </c>
       <c r="C87" s="37" t="inlineStr">
         <is>
-          <t>Crack and Fog Sealing Multiple Locations</t>
+          <t>EO</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
@@ -13694,17 +13814,17 @@
       </c>
       <c r="G87" s="20" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jul 27, 2026</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>32d</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
@@ -13721,102 +13841,102 @@
     <row r="88" ht="28" customHeight="1">
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>W50S9526BA002</t>
+          <t>SV0218-26</t>
         </is>
       </c>
       <c r="C88" s="40" t="inlineStr">
         <is>
-          <t>Repair and Widen Taxiways Phase III, PSTE 162013</t>
+          <t>Electrical Infrastructure Upgrade (Optics)</t>
         </is>
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
+          <t>Butner, North Carolina</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>Aug 05, 2026</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>41d</t>
+        </is>
+      </c>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>Solicitation</t>
+        </is>
+      </c>
+      <c r="K88" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="28" customHeight="1">
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>140P6426Q0073</t>
+        </is>
+      </c>
+      <c r="C89" s="37" t="inlineStr">
+        <is>
+          <t>Crack and Fog Sealing Multiple Locations</t>
+        </is>
+      </c>
+      <c r="D89" s="20" t="inlineStr">
+        <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E88" s="17" t="inlineStr">
+      <c r="E89" s="20" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F88" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G88" s="17" t="inlineStr">
-        <is>
-          <t>$22.5M</t>
-        </is>
-      </c>
-      <c r="H88" s="17" t="inlineStr">
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G89" s="20" t="inlineStr">
+        <is>
+          <t>$45.0M</t>
+        </is>
+      </c>
+      <c r="H89" s="20" t="inlineStr">
         <is>
           <t>Jun 25, 2026</t>
         </is>
       </c>
-      <c r="I88" s="17" t="inlineStr">
+      <c r="I89" s="20" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="J88" s="17" t="inlineStr">
+      <c r="J89" s="20" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K88" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="28" customHeight="1">
-      <c r="B89" s="23" t="inlineStr">
-        <is>
-          <t>W9128F26RA063</t>
-        </is>
-      </c>
-      <c r="C89" s="28" t="inlineStr">
-        <is>
-          <t>Fort Riley Tank CoatingsRepair</t>
-        </is>
-      </c>
-      <c r="D89" s="23" t="inlineStr">
-        <is>
-          <t>Fort Riley, Kansas</t>
-        </is>
-      </c>
-      <c r="E89" s="23" t="inlineStr">
-        <is>
-          <t>237120</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr">
-        <is>
-          <t>SDVOSB ★</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="I89" s="23" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="J89" s="23" t="inlineStr">
-        <is>
-          <t>Solicitation</t>
-        </is>
-      </c>
-      <c r="K89" s="36" t="inlineStr">
+      <c r="K89" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13825,12 +13945,12 @@
     <row r="90" ht="28" customHeight="1">
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>W911KB26RA039</t>
+          <t>W50S9526BA002</t>
         </is>
       </c>
       <c r="C90" s="40" t="inlineStr">
         <is>
-          <t>FTW506 Life Safety Repairs</t>
+          <t>Repair and Widen Taxiways Phase III, PSTE 162013</t>
         </is>
       </c>
       <c r="D90" s="17" t="inlineStr">
@@ -13840,7 +13960,7 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
@@ -13850,7 +13970,7 @@
       </c>
       <c r="G90" s="17" t="inlineStr">
         <is>
-          <t>$18.0M</t>
+          <t>$22.5M</t>
         </is>
       </c>
       <c r="H90" s="17" t="inlineStr">
@@ -13875,52 +13995,52 @@
       </c>
     </row>
     <row r="91" ht="28" customHeight="1">
-      <c r="B91" s="20" t="inlineStr">
-        <is>
-          <t>1605AE-26-Q-00005</t>
-        </is>
-      </c>
-      <c r="C91" s="37" t="inlineStr">
-        <is>
-          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
-        </is>
-      </c>
-      <c r="D91" s="20" t="inlineStr">
-        <is>
-          <t>Atlanta, Georgia</t>
-        </is>
-      </c>
-      <c r="E91" s="20" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F91" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G91" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H91" s="20" t="inlineStr">
+      <c r="B91" s="23" t="inlineStr">
+        <is>
+          <t>W9128F26RA063</t>
+        </is>
+      </c>
+      <c r="C91" s="28" t="inlineStr">
+        <is>
+          <t>Fort Riley Tank CoatingsRepair</t>
+        </is>
+      </c>
+      <c r="D91" s="23" t="inlineStr">
+        <is>
+          <t>Fort Riley, Kansas</t>
+        </is>
+      </c>
+      <c r="E91" s="23" t="inlineStr">
+        <is>
+          <t>237120</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>SDVOSB ★</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="23" t="inlineStr">
         <is>
           <t>Jun 25, 2026</t>
         </is>
       </c>
-      <c r="I91" s="20" t="inlineStr">
+      <c r="I91" s="23" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="J91" s="20" t="inlineStr">
+      <c r="J91" s="23" t="inlineStr">
         <is>
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="K91" s="39" t="inlineStr">
+      <c r="K91" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -13929,17 +14049,17 @@
     <row r="92" ht="28" customHeight="1">
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>FA469026Q0030</t>
+          <t>W911KB26RA039</t>
         </is>
       </c>
       <c r="C92" s="40" t="inlineStr">
         <is>
-          <t>Video Intercom System</t>
+          <t>FTW506 Life Safety Repairs</t>
         </is>
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t>Ellsworth AFB, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
@@ -13954,7 +14074,7 @@
       </c>
       <c r="G92" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$18.0M</t>
         </is>
       </c>
       <c r="H92" s="17" t="inlineStr">
@@ -13981,22 +14101,22 @@
     <row r="93" ht="28" customHeight="1">
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>W50S85-26-B-A007</t>
+          <t>1605AE-26-Q-00005</t>
         </is>
       </c>
       <c r="C93" s="37" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="E93" s="20" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -14011,17 +14131,17 @@
       </c>
       <c r="H93" s="20" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="I93" s="20" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="J93" s="20" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="K93" s="39" t="inlineStr">
@@ -14033,154 +14153,154 @@
     <row r="94" ht="28" customHeight="1">
       <c r="B94" s="17" t="inlineStr">
         <is>
+          <t>W50S85-26-B-A007</t>
+        </is>
+      </c>
+      <c r="C94" s="40" t="inlineStr">
+        <is>
+          <t>Feeder #7 Repair</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="inlineStr">
+        <is>
+          <t>Selfridge ANGB, Michigan</t>
+        </is>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>237130</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G94" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
+        <is>
+          <t>5d</t>
+        </is>
+      </c>
+      <c r="J94" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K94" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="28" customHeight="1">
+      <c r="B95" s="20" t="inlineStr">
+        <is>
           <t>W912DR26BA007</t>
         </is>
       </c>
-      <c r="C94" s="40" t="inlineStr">
+      <c r="C95" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">North East River Maintenance Dredging, Cecil County, MD </t>
         </is>
       </c>
-      <c r="D94" s="17" t="inlineStr">
+      <c r="D95" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E94" s="17" t="inlineStr">
+      <c r="E95" s="20" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="F94" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G94" s="17" t="inlineStr">
+      <c r="F95" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G95" s="20" t="inlineStr">
         <is>
           <t>$3.0M</t>
         </is>
       </c>
-      <c r="H94" s="17" t="inlineStr">
+      <c r="H95" s="20" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="I94" s="17" t="inlineStr">
+      <c r="I95" s="20" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="J94" s="17" t="inlineStr">
+      <c r="J95" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K94" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="28" customHeight="1">
-      <c r="B95" s="23" t="inlineStr">
+      <c r="K95" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="B96" s="23" t="inlineStr">
         <is>
           <t>36C24726Q0610</t>
         </is>
       </c>
-      <c r="C95" s="28" t="inlineStr">
+      <c r="C96" s="28" t="inlineStr">
         <is>
           <t>J041--Columbia South Carolina Boiler Plant Light Fixture  Repair Replacment Service  J041</t>
         </is>
       </c>
-      <c r="D95" s="23" t="inlineStr">
+      <c r="D96" s="23" t="inlineStr">
         <is>
           <t>Columbia, South Carolina</t>
         </is>
       </c>
-      <c r="E95" s="23" t="inlineStr">
+      <c r="E96" s="23" t="inlineStr">
         <is>
           <t>561210</t>
         </is>
       </c>
-      <c r="F95" s="23" t="inlineStr">
+      <c r="F96" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G95" s="23" t="inlineStr">
+      <c r="G96" s="23" t="inlineStr">
         <is>
           <t>$47.0M</t>
         </is>
       </c>
-      <c r="H95" s="23" t="inlineStr">
+      <c r="H96" s="23" t="inlineStr">
         <is>
           <t>Jul 01, 2026</t>
         </is>
       </c>
-      <c r="I95" s="23" t="inlineStr">
+      <c r="I96" s="23" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="J95" s="23" t="inlineStr">
+      <c r="J96" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K95" s="36" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="28" customHeight="1">
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
-        </is>
-      </c>
-      <c r="C96" s="40" t="inlineStr">
-        <is>
-          <t>Repair Hush House Concrete B3857</t>
-        </is>
-      </c>
-      <c r="D96" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E96" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F96" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G96" s="17" t="inlineStr">
-        <is>
-          <t>$23.0M</t>
-        </is>
-      </c>
-      <c r="H96" s="17" t="inlineStr">
-        <is>
-          <t>Jul 02, 2026</t>
-        </is>
-      </c>
-      <c r="I96" s="17" t="inlineStr">
-        <is>
-          <t>7d</t>
-        </is>
-      </c>
-      <c r="J96" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K96" s="42" t="inlineStr">
+      <c r="K96" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14189,154 +14309,154 @@
     <row r="97" ht="28" customHeight="1">
       <c r="B97" s="20" t="inlineStr">
         <is>
+          <t>W50S8526BA006_PROJECT_VGLZ262101</t>
+        </is>
+      </c>
+      <c r="C97" s="37" t="inlineStr">
+        <is>
+          <t>Repair Hush House Concrete B3857</t>
+        </is>
+      </c>
+      <c r="D97" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F97" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G97" s="20" t="inlineStr">
+        <is>
+          <t>$23.0M</t>
+        </is>
+      </c>
+      <c r="H97" s="20" t="inlineStr">
+        <is>
+          <t>Jul 02, 2026</t>
+        </is>
+      </c>
+      <c r="I97" s="20" t="inlineStr">
+        <is>
+          <t>7d</t>
+        </is>
+      </c>
+      <c r="J97" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K97" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="28" customHeight="1">
+      <c r="B98" s="17" t="inlineStr">
+        <is>
           <t>W9133L26BA010</t>
         </is>
       </c>
-      <c r="C97" s="37" t="inlineStr">
+      <c r="C98" s="40" t="inlineStr">
         <is>
           <t>Air National Guard (ANG) Smart Meters</t>
         </is>
       </c>
-      <c r="D97" s="20" t="inlineStr">
+      <c r="D98" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E97" s="20" t="inlineStr">
+      <c r="E98" s="17" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F97" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G97" s="20" t="inlineStr">
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
         <is>
           <t>$4.2M</t>
         </is>
       </c>
-      <c r="H97" s="20" t="inlineStr">
+      <c r="H98" s="17" t="inlineStr">
         <is>
           <t>Jul 02, 2026</t>
         </is>
       </c>
-      <c r="I97" s="20" t="inlineStr">
+      <c r="I98" s="17" t="inlineStr">
         <is>
           <t>7d</t>
         </is>
       </c>
-      <c r="J97" s="20" t="inlineStr">
+      <c r="J98" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K97" s="39" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="28" customHeight="1">
-      <c r="B98" s="23" t="inlineStr">
+      <c r="K98" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="B99" s="23" t="inlineStr">
         <is>
           <t>36C24626R0067</t>
         </is>
       </c>
-      <c r="C98" s="28" t="inlineStr">
+      <c r="C99" s="28" t="inlineStr">
         <is>
           <t>Z2DA--FY26 NRM  590-24-115 Public Address System</t>
         </is>
       </c>
-      <c r="D98" s="23" t="inlineStr">
+      <c r="D99" s="23" t="inlineStr">
         <is>
           <t>Hampton, Virginia</t>
         </is>
       </c>
-      <c r="E98" s="23" t="inlineStr">
+      <c r="E99" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F98" s="23" t="inlineStr">
+      <c r="F99" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G98" s="23" t="inlineStr">
+      <c r="G99" s="23" t="inlineStr">
         <is>
           <t>$7.0M</t>
         </is>
       </c>
-      <c r="H98" s="23" t="inlineStr">
+      <c r="H99" s="23" t="inlineStr">
         <is>
           <t>Jul 13, 2026</t>
         </is>
       </c>
-      <c r="I98" s="23" t="inlineStr">
+      <c r="I99" s="23" t="inlineStr">
         <is>
           <t>18d</t>
         </is>
       </c>
-      <c r="J98" s="23" t="inlineStr">
+      <c r="J99" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K98" s="36" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="28" customHeight="1">
-      <c r="B99" s="20" t="inlineStr">
-        <is>
-          <t>W912EE26RA015</t>
-        </is>
-      </c>
-      <c r="C99" s="37" t="inlineStr">
-        <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
-        </is>
-      </c>
-      <c r="D99" s="20" t="inlineStr">
-        <is>
-          <t>Royal, Arkansas</t>
-        </is>
-      </c>
-      <c r="E99" s="20" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F99" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G99" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H99" s="20" t="inlineStr">
-        <is>
-          <t>Jul 15, 2026</t>
-        </is>
-      </c>
-      <c r="I99" s="20" t="inlineStr">
-        <is>
-          <t>20d</t>
-        </is>
-      </c>
-      <c r="J99" s="20" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K99" s="39" t="inlineStr">
+      <c r="K99" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -14345,22 +14465,22 @@
     <row r="100" ht="28" customHeight="1">
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>140R4025R0017</t>
+          <t>W912EE26RA015</t>
         </is>
       </c>
       <c r="C100" s="40" t="inlineStr">
         <is>
-          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>561210</t>
         </is>
       </c>
       <c r="F100" s="17" t="inlineStr">
@@ -14375,12 +14495,12 @@
       </c>
       <c r="H100" s="17" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="J100" s="17" t="inlineStr">
@@ -14397,12 +14517,12 @@
     <row r="101" ht="28" customHeight="1">
       <c r="B101" s="20" t="inlineStr">
         <is>
-          <t>140L2626R0003</t>
+          <t>140R4025R0017</t>
         </is>
       </c>
       <c r="C101" s="37" t="inlineStr">
         <is>
-          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
+          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -14412,7 +14532,7 @@
       </c>
       <c r="E101" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
@@ -14427,12 +14547,12 @@
       </c>
       <c r="H101" s="20" t="inlineStr">
         <is>
-          <t>Jul 22, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="I101" s="20" t="inlineStr">
         <is>
-          <t>27d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="J101" s="20" t="inlineStr">
@@ -14449,12 +14569,12 @@
     <row r="102" ht="28" customHeight="1">
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>140L2626Q0033</t>
+          <t>140L2626R0003</t>
         </is>
       </c>
       <c r="C102" s="40" t="inlineStr">
         <is>
-          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
+          <t>Z--NORTH COTTEREL ROAD MAINTENANCE</t>
         </is>
       </c>
       <c r="D102" s="17" t="inlineStr">
@@ -14464,7 +14584,7 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F102" s="17" t="inlineStr">
@@ -14501,12 +14621,12 @@
     <row r="103" ht="28" customHeight="1">
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0016</t>
+          <t>140L2626Q0033</t>
         </is>
       </c>
       <c r="C103" s="37" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>Y--GAOA Milner Picnic Site Cabana Replacement</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
@@ -14516,7 +14636,7 @@
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -14531,12 +14651,12 @@
       </c>
       <c r="H103" s="20" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="I103" s="20" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="J103" s="20" t="inlineStr">
@@ -14553,12 +14673,12 @@
     <row r="104" ht="28" customHeight="1">
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>140P5426R0015</t>
+          <t>140P5426R0016</t>
         </is>
       </c>
       <c r="C104" s="40" t="inlineStr">
         <is>
-          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D104" s="17" t="inlineStr">
@@ -14568,7 +14688,7 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F104" s="17" t="inlineStr">
@@ -14605,12 +14725,12 @@
     <row r="105" ht="28" customHeight="1">
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>140P5426R0017</t>
+          <t>140P5426R0015</t>
         </is>
       </c>
       <c r="C105" s="37" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE PLANKS AND REPAIR PILINGS AT BODIE ISLAND LIGHTHOUSE BOARDWALK AND OBSE</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
@@ -14620,7 +14740,7 @@
       </c>
       <c r="E105" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -14657,22 +14777,22 @@
     <row r="106" ht="28" customHeight="1">
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>75H70126R00029</t>
+          <t>140P5426R0017</t>
         </is>
       </c>
       <c r="C106" s="40" t="inlineStr">
         <is>
-          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t>Pine Ridge, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
@@ -14682,17 +14802,17 @@
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H106" s="17" t="inlineStr">
         <is>
-          <t>Jul 31, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="J106" s="17" t="inlineStr">
@@ -14709,22 +14829,22 @@
     <row r="107" ht="28" customHeight="1">
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>140FGA26R0023</t>
+          <t>75H70126R00029</t>
         </is>
       </c>
       <c r="C107" s="37" t="inlineStr">
         <is>
-          <t>Y--Boat Ramp Replacement Project at Kirwin NWR</t>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
         <is>
-          <t>Kirwin, Kansas</t>
+          <t>Pine Ridge, South Dakota</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
@@ -14734,7 +14854,7 @@
       </c>
       <c r="G107" s="20" t="inlineStr">
         <is>
-          <t>$750K</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H107" s="20" t="inlineStr">
@@ -14761,258 +14881,258 @@
     <row r="108" ht="28" customHeight="1">
       <c r="B108" s="17" t="inlineStr">
         <is>
+          <t>140FGA26R0023</t>
+        </is>
+      </c>
+      <c r="C108" s="40" t="inlineStr">
+        <is>
+          <t>Y--Boat Ramp Replacement Project at Kirwin NWR</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="inlineStr">
+        <is>
+          <t>Kirwin, Kansas</t>
+        </is>
+      </c>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F108" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>$750K</t>
+        </is>
+      </c>
+      <c r="H108" s="17" t="inlineStr">
+        <is>
+          <t>Jul 31, 2026</t>
+        </is>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>36d</t>
+        </is>
+      </c>
+      <c r="J108" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K108" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="28" customHeight="1">
+      <c r="B109" s="20" t="inlineStr">
+        <is>
           <t>693C73-26-B-000017</t>
         </is>
       </c>
-      <c r="C108" s="40" t="inlineStr">
+      <c r="C109" s="37" t="inlineStr">
         <is>
           <t>Project VI NP VIIS 100(3) - Rehabilitation of Lameshur Road  in St. John, U.S. Virgin Islands</t>
         </is>
       </c>
-      <c r="D108" s="17" t="inlineStr">
+      <c r="D109" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E108" s="17" t="inlineStr">
+      <c r="E109" s="20" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F108" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G108" s="17" t="inlineStr">
+      <c r="F109" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G109" s="20" t="inlineStr">
         <is>
           <t>$2.5M</t>
         </is>
       </c>
-      <c r="H108" s="17" t="inlineStr">
+      <c r="H109" s="20" t="inlineStr">
         <is>
           <t>Aug 04, 2026</t>
         </is>
       </c>
-      <c r="I108" s="17" t="inlineStr">
+      <c r="I109" s="20" t="inlineStr">
         <is>
           <t>40d</t>
         </is>
       </c>
-      <c r="J108" s="17" t="inlineStr">
+      <c r="J109" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K108" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="28" customHeight="1">
-      <c r="B109" s="23" t="inlineStr">
+      <c r="K109" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="B110" s="23" t="inlineStr">
         <is>
           <t>36C25226B0029</t>
         </is>
       </c>
-      <c r="C109" s="28" t="inlineStr">
+      <c r="C110" s="28" t="inlineStr">
         <is>
           <t>Z1DA--556-24-113  Oil Transformer and Switch Enclosure Upgrades</t>
         </is>
       </c>
-      <c r="D109" s="23" t="inlineStr">
+      <c r="D110" s="23" t="inlineStr">
         <is>
           <t>North Chicago, Illinois</t>
         </is>
       </c>
-      <c r="E109" s="23" t="inlineStr">
+      <c r="E110" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F109" s="23" t="inlineStr">
+      <c r="F110" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G109" s="23" t="inlineStr">
+      <c r="G110" s="23" t="inlineStr">
         <is>
           <t>$3.5M</t>
         </is>
       </c>
-      <c r="H109" s="23" t="inlineStr">
+      <c r="H110" s="23" t="inlineStr">
         <is>
           <t>Aug 04, 2026</t>
         </is>
       </c>
-      <c r="I109" s="23" t="inlineStr">
+      <c r="I110" s="23" t="inlineStr">
         <is>
           <t>40d</t>
         </is>
       </c>
-      <c r="J109" s="23" t="inlineStr">
+      <c r="J110" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K109" s="36" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="28" customHeight="1">
-      <c r="B110" s="17" t="inlineStr">
+      <c r="K110" s="36" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="B111" s="20" t="inlineStr">
         <is>
           <t>140L3726R0006</t>
         </is>
       </c>
-      <c r="C110" s="40" t="inlineStr">
+      <c r="C111" s="37" t="inlineStr">
         <is>
           <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
-      <c r="D110" s="17" t="inlineStr">
+      <c r="D111" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E110" s="17" t="inlineStr">
+      <c r="E111" s="20" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F110" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G110" s="17" t="inlineStr">
+      <c r="F111" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G111" s="20" t="inlineStr">
         <is>
           <t>$19.0M</t>
         </is>
       </c>
-      <c r="H110" s="17" t="inlineStr">
+      <c r="H111" s="20" t="inlineStr">
         <is>
           <t>Aug 28, 2026</t>
         </is>
       </c>
-      <c r="I110" s="17" t="inlineStr">
+      <c r="I111" s="20" t="inlineStr">
         <is>
           <t>64d</t>
         </is>
       </c>
-      <c r="J110" s="17" t="inlineStr">
+      <c r="J111" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K110" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="B111" s="23" t="inlineStr">
+      <c r="K111" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="B112" s="23" t="inlineStr">
         <is>
           <t>36C25226B0031</t>
         </is>
       </c>
-      <c r="C111" s="28" t="inlineStr">
+      <c r="C112" s="28" t="inlineStr">
         <is>
           <t>Z1DA--ATTN GLAC SERVICES 537-25-102 Pyxis Cameras/Security  Renovations (VA-26-00016882)  FY26 NRM OS</t>
         </is>
       </c>
-      <c r="D111" s="23" t="inlineStr">
+      <c r="D112" s="23" t="inlineStr">
         <is>
           <t>Chicago, Illinois</t>
         </is>
       </c>
-      <c r="E111" s="23" t="inlineStr">
+      <c r="E112" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F111" s="23" t="inlineStr">
+      <c r="F112" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G111" s="23" t="inlineStr">
+      <c r="G112" s="23" t="inlineStr">
         <is>
           <t>$1.0B</t>
         </is>
       </c>
-      <c r="H111" s="23" t="inlineStr">
+      <c r="H112" s="23" t="inlineStr">
         <is>
           <t>Sep 03, 2026</t>
         </is>
       </c>
-      <c r="I111" s="23" t="inlineStr">
+      <c r="I112" s="23" t="inlineStr">
         <is>
           <t>70d</t>
         </is>
       </c>
-      <c r="J111" s="23" t="inlineStr">
+      <c r="J112" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K111" s="36" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="B112" s="17" t="inlineStr">
-        <is>
-          <t>140P8526Q0083</t>
-        </is>
-      </c>
-      <c r="C112" s="40" t="inlineStr">
-        <is>
-          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
-        </is>
-      </c>
-      <c r="D112" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E112" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F112" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G112" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H112" s="17" t="inlineStr">
-        <is>
-          <t>Jun 25, 2026</t>
-        </is>
-      </c>
-      <c r="I112" s="17" t="inlineStr">
-        <is>
-          <t>0d</t>
-        </is>
-      </c>
-      <c r="J112" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K112" s="42" t="inlineStr">
+      <c r="K112" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15021,12 +15141,12 @@
     <row r="113" ht="28" customHeight="1">
       <c r="B113" s="20" t="inlineStr">
         <is>
-          <t>140P9726Q0046</t>
+          <t>140P8526Q0083</t>
         </is>
       </c>
       <c r="C113" s="37" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>Y--YOSE-ROAD STRIPING BOF AND HWY 41</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -15036,7 +15156,7 @@
       </c>
       <c r="E113" s="20" t="inlineStr">
         <is>
-          <t>238210</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -15073,154 +15193,154 @@
     <row r="114" ht="28" customHeight="1">
       <c r="B114" s="17" t="inlineStr">
         <is>
+          <t>140P9726Q0046</t>
+        </is>
+      </c>
+      <c r="C114" s="40" t="inlineStr">
+        <is>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>238210</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G114" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H114" s="17" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026</t>
+        </is>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>0d</t>
+        </is>
+      </c>
+      <c r="J114" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K114" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="B115" s="20" t="inlineStr">
+        <is>
           <t>140P5326R0019</t>
         </is>
       </c>
-      <c r="C114" s="40" t="inlineStr">
+      <c r="C115" s="37" t="inlineStr">
         <is>
           <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
-      <c r="D114" s="17" t="inlineStr">
+      <c r="D115" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E114" s="17" t="inlineStr">
+      <c r="E115" s="20" t="inlineStr">
         <is>
           <t>237110</t>
         </is>
       </c>
-      <c r="F114" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G114" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H114" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I114" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J114" s="17" t="inlineStr">
+      <c r="F115" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G115" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H115" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J115" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K114" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="28" customHeight="1">
-      <c r="B115" s="23" t="inlineStr">
+      <c r="K115" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="B116" s="23" t="inlineStr">
         <is>
           <t>36C25726B0007</t>
         </is>
       </c>
-      <c r="C115" s="28" t="inlineStr">
+      <c r="C116" s="28" t="inlineStr">
         <is>
           <t>Y1DA--CON Project 674A4-21-108 - Upgrade Fire Alarm  System Campus Wide  (Waco) (VA-25-00021609)</t>
         </is>
       </c>
-      <c r="D115" s="23" t="inlineStr">
+      <c r="D116" s="23" t="inlineStr">
         <is>
           <t>Waco, Texas</t>
         </is>
       </c>
-      <c r="E115" s="23" t="inlineStr">
+      <c r="E116" s="23" t="inlineStr">
         <is>
           <t>238210</t>
         </is>
       </c>
-      <c r="F115" s="23" t="inlineStr">
+      <c r="F116" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G115" s="23" t="inlineStr">
+      <c r="G116" s="23" t="inlineStr">
         <is>
           <t>$2.5B</t>
         </is>
       </c>
-      <c r="H115" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I115" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J115" s="23" t="inlineStr">
+      <c r="H116" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J116" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K115" s="36" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="28" customHeight="1">
-      <c r="B116" s="17" t="inlineStr">
-        <is>
-          <t>W912HY26BA030</t>
-        </is>
-      </c>
-      <c r="C116" s="40" t="inlineStr">
-        <is>
-          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
-        </is>
-      </c>
-      <c r="D116" s="17" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E116" s="17" t="inlineStr">
-        <is>
-          <t>237990</t>
-        </is>
-      </c>
-      <c r="F116" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G116" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H116" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I116" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J116" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K116" s="42" t="inlineStr">
+      <c r="K116" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15229,17 +15349,17 @@
     <row r="117" ht="28" customHeight="1">
       <c r="B117" s="20" t="inlineStr">
         <is>
-          <t>W911WN26BA008</t>
+          <t>W912HY26BA030</t>
         </is>
       </c>
       <c r="C117" s="37" t="inlineStr">
         <is>
-          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
+          <t>HOUSTON SHIP CHANNEL, TEXAS, PLACEMENT AREA 14 DIKE RAISE</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>Saltsburg, Pennsylvania</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -15254,7 +15374,7 @@
       </c>
       <c r="G117" s="20" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H117" s="20" t="inlineStr">
@@ -15281,17 +15401,17 @@
     <row r="118" ht="28" customHeight="1">
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>PANNWD26P0000028054</t>
+          <t>W911WN26BA008</t>
         </is>
       </c>
       <c r="C118" s="40" t="inlineStr">
         <is>
-          <t>Levee Repair at MRLS L246</t>
+          <t>Conemaugh Dam Gantry Crane Machinery Housing Roof Replacement</t>
         </is>
       </c>
       <c r="D118" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Saltsburg, Pennsylvania</t>
         </is>
       </c>
       <c r="E118" s="17" t="inlineStr">
@@ -15306,7 +15426,7 @@
       </c>
       <c r="G118" s="17" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="H118" s="17" t="inlineStr">
@@ -15333,12 +15453,12 @@
     <row r="119" ht="28" customHeight="1">
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>140FGA26R0028</t>
+          <t>PANNWD26P0000028054</t>
         </is>
       </c>
       <c r="C119" s="37" t="inlineStr">
         <is>
-          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+          <t>Levee Repair at MRLS L246</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
@@ -15348,7 +15468,7 @@
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237990</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
@@ -15358,7 +15478,7 @@
       </c>
       <c r="G119" s="20" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="H119" s="20" t="inlineStr">
@@ -15385,154 +15505,154 @@
     <row r="120" ht="28" customHeight="1">
       <c r="B120" s="17" t="inlineStr">
         <is>
+          <t>140FGA26R0028</t>
+        </is>
+      </c>
+      <c r="C120" s="40" t="inlineStr">
+        <is>
+          <t>Z--PR-CULEBRA NWR-ROAD &amp; PARKING REHAB</t>
+        </is>
+      </c>
+      <c r="D120" s="17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F120" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G120" s="17" t="inlineStr">
+        <is>
+          <t>$11.8M</t>
+        </is>
+      </c>
+      <c r="H120" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J120" s="17" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K120" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="28" customHeight="1">
+      <c r="B121" s="20" t="inlineStr">
+        <is>
           <t>W9128F26RA107</t>
         </is>
       </c>
-      <c r="C120" s="40" t="inlineStr">
+      <c r="C121" s="37" t="inlineStr">
         <is>
           <t>Repair/Replace Mass Parking Apron Section V at Minot AFB North Dakota</t>
         </is>
       </c>
-      <c r="D120" s="17" t="inlineStr">
+      <c r="D121" s="20" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E120" s="17" t="inlineStr">
+      <c r="E121" s="20" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F120" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G120" s="17" t="inlineStr">
+      <c r="F121" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G121" s="20" t="inlineStr">
         <is>
           <t>$30.0M</t>
         </is>
       </c>
-      <c r="H120" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I120" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J120" s="17" t="inlineStr">
+      <c r="H121" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I121" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J121" s="20" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K120" s="42" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="28" customHeight="1">
-      <c r="B121" s="23" t="inlineStr">
+      <c r="K121" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="B122" s="23" t="inlineStr">
         <is>
           <t>36C24226B0057</t>
         </is>
       </c>
-      <c r="C121" s="28" t="inlineStr">
+      <c r="C122" s="28" t="inlineStr">
         <is>
           <t>N091--PROJECT # 528-18-110  Fuel Oil Tank Replacement  BUFFALO VAMC</t>
         </is>
       </c>
-      <c r="D121" s="23" t="inlineStr">
+      <c r="D122" s="23" t="inlineStr">
         <is>
           <t>Buffalo, New York</t>
         </is>
       </c>
-      <c r="E121" s="23" t="inlineStr">
+      <c r="E122" s="23" t="inlineStr">
         <is>
           <t>237120</t>
         </is>
       </c>
-      <c r="F121" s="23" t="inlineStr">
+      <c r="F122" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G121" s="23" t="inlineStr">
+      <c r="G122" s="23" t="inlineStr">
         <is>
           <t>$16.2M</t>
         </is>
       </c>
-      <c r="H121" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I121" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J121" s="23" t="inlineStr">
+      <c r="H122" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J122" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K121" s="36" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="28" customHeight="1">
-      <c r="B122" s="17" t="inlineStr">
-        <is>
-          <t>140P6326B0008</t>
-        </is>
-      </c>
-      <c r="C122" s="40" t="inlineStr">
-        <is>
-          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
-        </is>
-      </c>
-      <c r="D122" s="17" t="inlineStr">
-        <is>
-          <t>Medora, North Dakota</t>
-        </is>
-      </c>
-      <c r="E122" s="17" t="inlineStr">
-        <is>
-          <t>237310</t>
-        </is>
-      </c>
-      <c r="F122" s="17" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G122" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H122" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I122" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J122" s="17" t="inlineStr">
-        <is>
-          <t>Presolicitation</t>
-        </is>
-      </c>
-      <c r="K122" s="42" t="inlineStr">
+      <c r="K122" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15541,22 +15661,22 @@
     <row r="123" ht="28" customHeight="1">
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>W912DQ26QA063</t>
+          <t>140P6326B0008</t>
         </is>
       </c>
       <c r="C123" s="37" t="inlineStr">
         <is>
-          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+          <t>Z--Theodore Roosevelt National Park- Restripe Park Roads/Install Speed Humps/Apply</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>Stockton, Missouri</t>
+          <t>Medora, North Dakota</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
         <is>
-          <t>237110</t>
+          <t>237310</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
@@ -15593,22 +15713,22 @@
     <row r="124" ht="28" customHeight="1">
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>W912WJ26QA124</t>
+          <t>W912DQ26QA063</t>
         </is>
       </c>
       <c r="C124" s="40" t="inlineStr">
         <is>
-          <t>Road Gate Painting, Road Gate Installation, Removal and Replacement of Guardrails, Buffumville Lake, Charlton, MA</t>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
         </is>
       </c>
       <c r="D124" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Stockton, Missouri</t>
         </is>
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>237310</t>
+          <t>237110</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
@@ -15618,7 +15738,7 @@
       </c>
       <c r="G124" s="17" t="inlineStr">
         <is>
-          <t>$175K</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H124" s="17" t="inlineStr">
@@ -15645,154 +15765,154 @@
     <row r="125" ht="28" customHeight="1">
       <c r="B125" s="20" t="inlineStr">
         <is>
+          <t>W912WJ26QA124</t>
+        </is>
+      </c>
+      <c r="C125" s="37" t="inlineStr">
+        <is>
+          <t>Road Gate Painting, Road Gate Installation, Removal and Replacement of Guardrails, Buffumville Lake, Charlton, MA</t>
+        </is>
+      </c>
+      <c r="D125" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E125" s="20" t="inlineStr">
+        <is>
+          <t>237310</t>
+        </is>
+      </c>
+      <c r="F125" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G125" s="20" t="inlineStr">
+        <is>
+          <t>$175K</t>
+        </is>
+      </c>
+      <c r="H125" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I125" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J125" s="20" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="K125" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="B126" s="17" t="inlineStr">
+        <is>
           <t>W9123826RA018</t>
         </is>
       </c>
-      <c r="C125" s="37" t="inlineStr">
+      <c r="C126" s="40" t="inlineStr">
         <is>
           <t>USACE SPK DB Construction – DDJC Centralized Gas and Electric Metering - Tracy, CA</t>
         </is>
       </c>
-      <c r="D125" s="20" t="inlineStr">
+      <c r="D126" s="17" t="inlineStr">
         <is>
           <t>Tracy, California</t>
         </is>
       </c>
-      <c r="E125" s="20" t="inlineStr">
+      <c r="E126" s="17" t="inlineStr">
         <is>
           <t>237130</t>
         </is>
       </c>
-      <c r="F125" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G125" s="20" t="inlineStr">
+      <c r="F126" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G126" s="17" t="inlineStr">
         <is>
           <t>$7.5M</t>
         </is>
       </c>
-      <c r="H125" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I125" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J125" s="20" t="inlineStr">
+      <c r="H126" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J126" s="17" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K125" s="39" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="28" customHeight="1">
-      <c r="B126" s="23" t="inlineStr">
+      <c r="K126" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="B127" s="23" t="inlineStr">
         <is>
           <t>36C78626B0023</t>
         </is>
       </c>
-      <c r="C126" s="28" t="inlineStr">
+      <c r="C127" s="28" t="inlineStr">
         <is>
           <t>CORINTH NATIONAL CEMETERY, 838CM3036 – GRAVESITE EXPANSION AND CEMETERY IMPROVEMENTS</t>
         </is>
       </c>
-      <c r="D126" s="23" t="inlineStr">
+      <c r="D127" s="23" t="inlineStr">
         <is>
           <t>Corinth, Mississippi</t>
         </is>
       </c>
-      <c r="E126" s="23" t="inlineStr">
+      <c r="E127" s="23" t="inlineStr">
         <is>
           <t>237990</t>
         </is>
       </c>
-      <c r="F126" s="23" t="inlineStr">
+      <c r="F127" s="23" t="inlineStr">
         <is>
           <t>SDVOSB ★</t>
         </is>
       </c>
-      <c r="G126" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H126" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I126" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J126" s="23" t="inlineStr">
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H127" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I127" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J127" s="23" t="inlineStr">
         <is>
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="K126" s="36" t="inlineStr">
-        <is>
-          <t>SAM.gov ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="28" customHeight="1">
-      <c r="B127" s="20" t="inlineStr">
-        <is>
-          <t>SP470525R002026</t>
-        </is>
-      </c>
-      <c r="C127" s="37" t="inlineStr">
-        <is>
-          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
-        </is>
-      </c>
-      <c r="D127" s="20" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="E127" s="20" t="inlineStr">
-        <is>
-          <t>561210</t>
-        </is>
-      </c>
-      <c r="F127" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G127" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H127" s="20" t="inlineStr">
-        <is>
-          <t>Jun 30, 2026</t>
-        </is>
-      </c>
-      <c r="I127" s="20" t="inlineStr">
-        <is>
-          <t>5d</t>
-        </is>
-      </c>
-      <c r="J127" s="20" t="inlineStr">
-        <is>
-          <t>Special Notice</t>
-        </is>
-      </c>
-      <c r="K127" s="39" t="inlineStr">
+      <c r="K127" s="36" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
@@ -15801,17 +15921,17 @@
     <row r="128" ht="28" customHeight="1">
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>140R6026R0016</t>
+          <t>1305M4-26-R-0034</t>
         </is>
       </c>
       <c r="C128" s="40" t="inlineStr">
         <is>
-          <t>Z--Webster Dam, Spillway Radial Gates Repair, Webster Unit, Solomon Division, Pick</t>
+          <t>Design-Build Repair and Renovation of the Gulf Marine Service Facility (GMSF) &amp; Wharf Repairs, in Pascagoula, Mississippi</t>
         </is>
       </c>
       <c r="D128" s="17" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Pascagoula, Mississippi</t>
         </is>
       </c>
       <c r="E128" s="17" t="inlineStr">
@@ -15826,22 +15946,22 @@
       </c>
       <c r="G128" s="17" t="inlineStr">
         <is>
-          <t>$7.5M</t>
+          <t>$23.5M</t>
         </is>
       </c>
       <c r="H128" s="17" t="inlineStr">
         <is>
-          <t>Aug 10, 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
-          <t>46d</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J128" s="17" t="inlineStr">
         <is>
-          <t>Special Notice</t>
+          <t>Presolicitation</t>
         </is>
       </c>
       <c r="K128" s="42" t="inlineStr">
@@ -15853,57 +15973,161 @@
     <row r="129" ht="28" customHeight="1">
       <c r="B129" s="20" t="inlineStr">
         <is>
+          <t>SP470525R002026</t>
+        </is>
+      </c>
+      <c r="C129" s="37" t="inlineStr">
+        <is>
+          <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
+        </is>
+      </c>
+      <c r="D129" s="20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="E129" s="20" t="inlineStr">
+        <is>
+          <t>561210</t>
+        </is>
+      </c>
+      <c r="F129" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G129" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H129" s="20" t="inlineStr">
+        <is>
+          <t>Jun 30, 2026</t>
+        </is>
+      </c>
+      <c r="I129" s="20" t="inlineStr">
+        <is>
+          <t>5d</t>
+        </is>
+      </c>
+      <c r="J129" s="20" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K129" s="39" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="B130" s="17" t="inlineStr">
+        <is>
+          <t>140R6026R0016</t>
+        </is>
+      </c>
+      <c r="C130" s="40" t="inlineStr">
+        <is>
+          <t>Z--Webster Dam, Spillway Radial Gates Repair, Webster Unit, Solomon Division, Pick</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>237990</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G130" s="17" t="inlineStr">
+        <is>
+          <t>$7.5M</t>
+        </is>
+      </c>
+      <c r="H130" s="17" t="inlineStr">
+        <is>
+          <t>Aug 10, 2026</t>
+        </is>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>46d</t>
+        </is>
+      </c>
+      <c r="J130" s="17" t="inlineStr">
+        <is>
+          <t>Special Notice</t>
+        </is>
+      </c>
+      <c r="K130" s="42" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="B131" s="20" t="inlineStr">
+        <is>
           <t>W9127826RA025</t>
         </is>
       </c>
-      <c r="C129" s="37" t="inlineStr">
+      <c r="C131" s="37" t="inlineStr">
         <is>
           <t>Phillips Parkway Haul Route</t>
         </is>
       </c>
-      <c r="D129" s="20" t="inlineStr">
+      <c r="D131" s="20" t="inlineStr">
         <is>
           <t>Cape Canaveral, Florida</t>
         </is>
       </c>
-      <c r="E129" s="20" t="inlineStr">
+      <c r="E131" s="20" t="inlineStr">
         <is>
           <t>237310</t>
         </is>
       </c>
-      <c r="F129" s="20" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="G129" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H129" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I129" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J129" s="20" t="inlineStr">
+      <c r="F131" s="20" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="G131" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H131" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I131" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J131" s="20" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="K129" s="39" t="inlineStr">
+      <c r="K131" s="39" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K129"/>
+  <autoFilter ref="B5:K131"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -16033,6 +16257,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16045,7 +16271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K71"/>
+  <dimension ref="B2:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -16073,7 +16299,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="47" t="inlineStr">
         <is>
-          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  66 records  (10 SDVOSB)  ·  June 24, 2026</t>
+          <t>NAICS: 213112 · 237110 · 237120 · 237130 · 238210 · 561210  ·  67 records  (10 SDVOSB)  ·  June 24, 2026</t>
         </is>
       </c>
     </row>
@@ -17017,17 +17243,17 @@
     <row r="23" ht="28" customHeight="1">
       <c r="B23" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C23" s="55" t="inlineStr">
         <is>
-          <t>Shenango River Lake Water Tank Rehabiliation</t>
+          <t>Electrical Upgrade for Brass Crusher</t>
         </is>
       </c>
       <c r="D23" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Tampa, Florida</t>
         </is>
       </c>
       <c r="E23" s="56" t="inlineStr">
@@ -17037,7 +17263,7 @@
       </c>
       <c r="F23" s="56" t="inlineStr">
         <is>
-          <t>$45.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="56" t="inlineStr">
@@ -17074,12 +17300,12 @@
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>Electrical Upgrade for Brass Crusher</t>
+          <t>Fiber Optic Cable Replacement</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>Tampa, Florida</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
@@ -17121,12 +17347,12 @@
     <row r="25" ht="28" customHeight="1">
       <c r="B25" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C25" s="55" t="inlineStr">
         <is>
-          <t>Fiber Optic Cable Replacement</t>
+          <t>Y--GLBA REHAB WATERLINE</t>
         </is>
       </c>
       <c r="D25" s="56" t="inlineStr">
@@ -17146,12 +17372,12 @@
       </c>
       <c r="G25" s="56" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jul 01, 2026</t>
         </is>
       </c>
       <c r="H25" s="56" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>6d</t>
         </is>
       </c>
       <c r="I25" s="56" t="inlineStr">
@@ -17173,12 +17399,12 @@
     <row r="26" ht="28" customHeight="1">
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
-          <t>Y--GLBA REHAB WATERLINE</t>
+          <t>N-- AIRR Security Cameras &amp; Badging for BTFA</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
@@ -17225,12 +17451,12 @@
     <row r="27" ht="28" customHeight="1">
       <c r="B27" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C27" s="55" t="inlineStr">
         <is>
-          <t>N-- AIRR Security Cameras &amp; Badging for BTFA</t>
+          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
         </is>
       </c>
       <c r="D27" s="56" t="inlineStr">
@@ -17245,17 +17471,17 @@
       </c>
       <c r="F27" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.4M</t>
         </is>
       </c>
       <c r="G27" s="56" t="inlineStr">
         <is>
-          <t>Jul 01, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="H27" s="56" t="inlineStr">
         <is>
-          <t>6d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="I27" s="56" t="inlineStr">
@@ -17277,12 +17503,12 @@
     <row r="28" ht="28" customHeight="1">
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>Telecom lines replacement, Lake Roosevelt NRA</t>
+          <t>NOAA Western Regional Center H32 Electrical Repair</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
@@ -17297,7 +17523,7 @@
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>$11.4M</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
@@ -17334,12 +17560,12 @@
       </c>
       <c r="C29" s="55" t="inlineStr">
         <is>
-          <t>NOAA Western Regional Center H32 Electrical Repair</t>
+          <t>Video Intercom System</t>
         </is>
       </c>
       <c r="D29" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Ellsworth AFB, South Dakota</t>
         </is>
       </c>
       <c r="E29" s="56" t="inlineStr">
@@ -17349,17 +17575,17 @@
       </c>
       <c r="F29" s="56" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="56" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jul 03, 2026</t>
         </is>
       </c>
       <c r="H29" s="56" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="I29" s="56" t="inlineStr">
@@ -18317,12 +18543,12 @@
     <row r="48" ht="28" customHeight="1">
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C48" s="40" t="inlineStr">
         <is>
-          <t>Beresford Substation Stage 11, South Dakota</t>
+          <t>Shenango River Lake Water Tank Rehabiliation</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
@@ -18337,17 +18563,17 @@
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$45.0M</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 14, 2026</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
@@ -18369,12 +18595,12 @@
     <row r="49" ht="28" customHeight="1">
       <c r="B49" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C49" s="55" t="inlineStr">
         <is>
-          <t>Y--FORT HOWES WATER STORAGE TANK</t>
+          <t>Beresford Substation Stage 11, South Dakota</t>
         </is>
       </c>
       <c r="D49" s="56" t="inlineStr">
@@ -18421,17 +18647,17 @@
     <row r="50" ht="28" customHeight="1">
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C50" s="40" t="inlineStr">
         <is>
-          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
+          <t>Y--FORT HOWES WATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t>Jefferson, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
@@ -18473,17 +18699,17 @@
     <row r="51" ht="28" customHeight="1">
       <c r="B51" s="54" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C51" s="55" t="inlineStr">
         <is>
-          <t>Water Tank Storage</t>
+          <t>National Center for Toxicological Research (NCTR) on-site facility Operations and Maintenance (O&amp;M) support services</t>
         </is>
       </c>
       <c r="D51" s="56" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Jefferson, Arkansas</t>
         </is>
       </c>
       <c r="E51" s="56" t="inlineStr">
@@ -18498,12 +18724,12 @@
       </c>
       <c r="G51" s="56" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H51" s="56" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="I51" s="56" t="inlineStr">
@@ -18530,7 +18756,7 @@
       </c>
       <c r="C52" s="40" t="inlineStr">
         <is>
-          <t>LARO-DRILL NEW WATER WELL - SHERMAN HOMES CABINS</t>
+          <t>Water Tank Storage</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
@@ -18550,12 +18776,12 @@
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>Jul 17, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>22d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
@@ -18582,12 +18808,12 @@
       </c>
       <c r="C53" s="55" t="inlineStr">
         <is>
-          <t>Rosebud Lift Station Construction</t>
+          <t>LARO-DRILL NEW WATER WELL - SHERMAN HOMES CABINS</t>
         </is>
       </c>
       <c r="D53" s="56" t="inlineStr">
         <is>
-          <t>Rosebud, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E53" s="56" t="inlineStr">
@@ -18597,17 +18823,17 @@
       </c>
       <c r="F53" s="56" t="inlineStr">
         <is>
-          <t>$11.8M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="56" t="inlineStr">
         <is>
-          <t>Jul 20, 2026</t>
+          <t>Jul 17, 2026</t>
         </is>
       </c>
       <c r="H53" s="56" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>22d</t>
         </is>
       </c>
       <c r="I53" s="56" t="inlineStr">
@@ -18629,17 +18855,17 @@
     <row r="54" ht="28" customHeight="1">
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C54" s="40" t="inlineStr">
         <is>
-          <t>B16 PLC Replacement</t>
+          <t>Rosebud Lift Station Construction</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Rosebud, South Dakota</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
@@ -18649,17 +18875,17 @@
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$11.8M</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 20, 2026</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>25d</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
@@ -18681,17 +18907,17 @@
     <row r="55" ht="28" customHeight="1">
       <c r="B55" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237120 — Oil &amp; Gas Pipeline</t>
         </is>
       </c>
       <c r="C55" s="55" t="inlineStr">
         <is>
-          <t>Electrical Infrastructure Upgrade (Optics)</t>
+          <t>FMC Rochester Install Above Ground Tanks</t>
         </is>
       </c>
       <c r="D55" s="56" t="inlineStr">
         <is>
-          <t>Butner, North Carolina</t>
+          <t>Rochester, Minnesota</t>
         </is>
       </c>
       <c r="E55" s="56" t="inlineStr">
@@ -18701,17 +18927,17 @@
       </c>
       <c r="F55" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$375K</t>
         </is>
       </c>
       <c r="G55" s="56" t="inlineStr">
         <is>
-          <t>Aug 05, 2026</t>
+          <t>Jul 22, 2026</t>
         </is>
       </c>
       <c r="H55" s="56" t="inlineStr">
         <is>
-          <t>41d</t>
+          <t>27d</t>
         </is>
       </c>
       <c r="I55" s="56" t="inlineStr">
@@ -18719,9 +18945,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J55" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J55" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K55" s="57" t="inlineStr">
@@ -18738,7 +18964,7 @@
       </c>
       <c r="C56" s="40" t="inlineStr">
         <is>
-          <t>FTW506 Life Safety Repairs</t>
+          <t>B16 PLC Replacement</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
@@ -18753,17 +18979,17 @@
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>$18.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
@@ -18771,9 +18997,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J56" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J56" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K56" s="42" t="inlineStr">
@@ -18785,17 +19011,17 @@
     <row r="57" ht="28" customHeight="1">
       <c r="B57" s="54" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C57" s="55" t="inlineStr">
         <is>
-          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
+          <t>Electrical Infrastructure Upgrade (Optics)</t>
         </is>
       </c>
       <c r="D57" s="56" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia</t>
+          <t>Butner, North Carolina</t>
         </is>
       </c>
       <c r="E57" s="56" t="inlineStr">
@@ -18810,12 +19036,12 @@
       </c>
       <c r="G57" s="56" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Aug 05, 2026</t>
         </is>
       </c>
       <c r="H57" s="56" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>41d</t>
         </is>
       </c>
       <c r="I57" s="56" t="inlineStr">
@@ -18823,9 +19049,9 @@
           <t>Solicitation</t>
         </is>
       </c>
-      <c r="J57" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J57" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K57" s="57" t="inlineStr">
@@ -18842,12 +19068,12 @@
       </c>
       <c r="C58" s="40" t="inlineStr">
         <is>
-          <t>Video Intercom System</t>
+          <t>FTW506 Life Safety Repairs</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>Ellsworth AFB, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
@@ -18857,7 +19083,7 @@
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$18.0M</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -18889,17 +19115,17 @@
     <row r="59" ht="28" customHeight="1">
       <c r="B59" s="54" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C59" s="55" t="inlineStr">
         <is>
-          <t>Feeder #7 Repair</t>
+          <t>Atlanta Job Corps Center Caretaker and Security Services</t>
         </is>
       </c>
       <c r="D59" s="56" t="inlineStr">
         <is>
-          <t>Selfridge ANGB, Michigan</t>
+          <t>Atlanta, Georgia</t>
         </is>
       </c>
       <c r="E59" s="56" t="inlineStr">
@@ -18914,17 +19140,17 @@
       </c>
       <c r="G59" s="56" t="inlineStr">
         <is>
-          <t>Jun 30, 2026</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="H59" s="56" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I59" s="56" t="inlineStr">
         <is>
-          <t>Presolicitation</t>
+          <t>Solicitation</t>
         </is>
       </c>
       <c r="J59" s="18" t="inlineStr">
@@ -18941,17 +19167,17 @@
     <row r="60" ht="28" customHeight="1">
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237130 — Power &amp; Communication Line</t>
         </is>
       </c>
       <c r="C60" s="40" t="inlineStr">
         <is>
-          <t>Air National Guard (ANG) Smart Meters</t>
+          <t>Feeder #7 Repair</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Selfridge ANGB, Michigan</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
@@ -18961,17 +19187,17 @@
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>$4.2M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>Jul 02, 2026</t>
+          <t>Jun 30, 2026</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>5d</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
@@ -18993,17 +19219,17 @@
     <row r="61" ht="28" customHeight="1">
       <c r="B61" s="54" t="inlineStr">
         <is>
-          <t>561210 — Facilities Maintenance</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C61" s="55" t="inlineStr">
         <is>
-          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
+          <t>Air National Guard (ANG) Smart Meters</t>
         </is>
       </c>
       <c r="D61" s="56" t="inlineStr">
         <is>
-          <t>Royal, Arkansas</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E61" s="56" t="inlineStr">
@@ -19013,17 +19239,17 @@
       </c>
       <c r="F61" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$4.2M</t>
         </is>
       </c>
       <c r="G61" s="56" t="inlineStr">
         <is>
-          <t>Jul 15, 2026</t>
+          <t>Jul 02, 2026</t>
         </is>
       </c>
       <c r="H61" s="56" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>7d</t>
         </is>
       </c>
       <c r="I61" s="56" t="inlineStr">
@@ -19031,9 +19257,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J61" s="43" t="inlineStr">
-        <is>
-          <t>🟡 Soon</t>
+      <c r="J61" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K61" s="57" t="inlineStr">
@@ -19045,17 +19271,17 @@
     <row r="62" ht="28" customHeight="1">
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
       <c r="C62" s="40" t="inlineStr">
         <is>
-          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
+          <t>Indefinite Delivery/Indefinite Quantity (IDIQ), Operation and Maintenance of Arkansas Lakes at Lake Ouachita, Lake Greeson, and DeGray Lake</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Royal, Arkansas</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
@@ -19070,12 +19296,12 @@
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Jul 15, 2026</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>21d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
@@ -19102,7 +19328,7 @@
       </c>
       <c r="C63" s="55" t="inlineStr">
         <is>
-          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
+          <t>C--BGNDRF YARD PIPING &amp; FLOW MEASUREMENT UPGRADES</t>
         </is>
       </c>
       <c r="D63" s="56" t="inlineStr">
@@ -19122,12 +19348,12 @@
       </c>
       <c r="G63" s="56" t="inlineStr">
         <is>
-          <t>Jul 24, 2026</t>
+          <t>Jul 16, 2026</t>
         </is>
       </c>
       <c r="H63" s="56" t="inlineStr">
         <is>
-          <t>29d</t>
+          <t>21d</t>
         </is>
       </c>
       <c r="I63" s="56" t="inlineStr">
@@ -19154,7 +19380,7 @@
       </c>
       <c r="C64" s="40" t="inlineStr">
         <is>
-          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
+          <t>Z--REPLACE BACKFLOW PREVENTER ON LIGHTHOUSE ROAD AT CAPE HATTERAS NATIONAL SEASHORE</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -19201,17 +19427,17 @@
     <row r="65" ht="28" customHeight="1">
       <c r="B65" s="54" t="inlineStr">
         <is>
-          <t>238210 — Electrical Contractors</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C65" s="55" t="inlineStr">
         <is>
-          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
+          <t>Z--CYCLIC MAINTENANCE OF WATER CISTERNS AT DRY TORTUGAS NATIONAL PARK</t>
         </is>
       </c>
       <c r="D65" s="56" t="inlineStr">
         <is>
-          <t>Pine Ridge, South Dakota</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E65" s="56" t="inlineStr">
@@ -19221,17 +19447,17 @@
       </c>
       <c r="F65" s="56" t="inlineStr">
         <is>
-          <t>$3.0M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G65" s="56" t="inlineStr">
         <is>
-          <t>Jul 31, 2026</t>
+          <t>Jul 24, 2026</t>
         </is>
       </c>
       <c r="H65" s="56" t="inlineStr">
         <is>
-          <t>36d</t>
+          <t>29d</t>
         </is>
       </c>
       <c r="I65" s="56" t="inlineStr">
@@ -19239,9 +19465,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J65" s="44" t="inlineStr">
-        <is>
-          <t>⬜ Watch</t>
+      <c r="J65" s="43" t="inlineStr">
+        <is>
+          <t>🟡 Soon</t>
         </is>
       </c>
       <c r="K65" s="57" t="inlineStr">
@@ -19258,12 +19484,12 @@
       </c>
       <c r="C66" s="40" t="inlineStr">
         <is>
-          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
+          <t>LED Lighting Replacement at Pine Ridge Hospital</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Pine Ridge, South Dakota</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -19273,17 +19499,17 @@
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>$19.0M</t>
+          <t>$3.0M</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Jul 31, 2026</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>64d</t>
+          <t>36d</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
@@ -19310,7 +19536,7 @@
       </c>
       <c r="C67" s="55" t="inlineStr">
         <is>
-          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
+          <t>Z--NIFC 410B RSC FIRE ALARM REPLACE</t>
         </is>
       </c>
       <c r="D67" s="56" t="inlineStr">
@@ -19325,17 +19551,17 @@
       </c>
       <c r="F67" s="56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$19.0M</t>
         </is>
       </c>
       <c r="G67" s="56" t="inlineStr">
         <is>
-          <t>Jun 25, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="H67" s="56" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>64d</t>
         </is>
       </c>
       <c r="I67" s="56" t="inlineStr">
@@ -19343,9 +19569,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J67" s="18" t="inlineStr">
-        <is>
-          <t>🔴 Urgent</t>
+      <c r="J67" s="44" t="inlineStr">
+        <is>
+          <t>⬜ Watch</t>
         </is>
       </c>
       <c r="K67" s="57" t="inlineStr">
@@ -19357,12 +19583,12 @@
     <row r="68" ht="28" customHeight="1">
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>237110 — Water &amp; Sewer</t>
+          <t>238210 — Electrical Contractors</t>
         </is>
       </c>
       <c r="C68" s="40" t="inlineStr">
         <is>
-          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
+          <t>N--EO14398 ELECTRIC REPAIRS AT SIX ALASKAN N. PARKS</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
@@ -19382,12 +19608,12 @@
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jun 25, 2026</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
@@ -19395,9 +19621,9 @@
           <t>Presolicitation</t>
         </is>
       </c>
-      <c r="J68" s="44" t="inlineStr">
-        <is>
-          <t>Pre-Sol</t>
+      <c r="J68" s="18" t="inlineStr">
+        <is>
+          <t>🔴 Urgent</t>
         </is>
       </c>
       <c r="K68" s="42" t="inlineStr">
@@ -19414,12 +19640,12 @@
       </c>
       <c r="C69" s="55" t="inlineStr">
         <is>
-          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
+          <t>Y--GRSM NEWFOUND GAP WASTEWATER SYSTEM WORK</t>
         </is>
       </c>
       <c r="D69" s="56" t="inlineStr">
         <is>
-          <t>Stockton, Missouri</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="E69" s="56" t="inlineStr">
@@ -19461,17 +19687,17 @@
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>237130 — Power &amp; Communication Line</t>
+          <t>237110 — Water &amp; Sewer</t>
         </is>
       </c>
       <c r="C70" s="40" t="inlineStr">
         <is>
-          <t>USACE SPK DB Construction – DDJC Centralized Gas and Electric Metering - Tracy, CA</t>
+          <t>ODF-S FY26 Hawker Point North Well Casing Repair</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>Tracy, California</t>
+          <t>Stockton, Missouri</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -19481,7 +19707,7 @@
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>$7.5M</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
@@ -19513,57 +19739,109 @@
     <row r="71" ht="28" customHeight="1">
       <c r="B71" s="54" t="inlineStr">
         <is>
+          <t>237130 — Power &amp; Communication Line</t>
+        </is>
+      </c>
+      <c r="C71" s="55" t="inlineStr">
+        <is>
+          <t>USACE SPK DB Construction – DDJC Centralized Gas and Electric Metering - Tracy, CA</t>
+        </is>
+      </c>
+      <c r="D71" s="56" t="inlineStr">
+        <is>
+          <t>Tracy, California</t>
+        </is>
+      </c>
+      <c r="E71" s="56" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F71" s="56" t="inlineStr">
+        <is>
+          <t>$7.5M</t>
+        </is>
+      </c>
+      <c r="G71" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="56" t="inlineStr">
+        <is>
+          <t>Presolicitation</t>
+        </is>
+      </c>
+      <c r="J71" s="44" t="inlineStr">
+        <is>
+          <t>Pre-Sol</t>
+        </is>
+      </c>
+      <c r="K71" s="57" t="inlineStr">
+        <is>
+          <t>SAM.gov ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="B72" s="16" t="inlineStr">
+        <is>
           <t>561210 — Facilities Maintenance</t>
         </is>
       </c>
-      <c r="C71" s="55" t="inlineStr">
+      <c r="C72" s="40" t="inlineStr">
         <is>
           <t>Special Notice: Forthcoming Solicitation for Building Control System (BCS) and Utility Control System (UCS) Maintenance and Support Services</t>
         </is>
       </c>
-      <c r="D71" s="56" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>Not Specified</t>
         </is>
       </c>
-      <c r="E71" s="56" t="inlineStr">
-        <is>
-          <t>SBA</t>
-        </is>
-      </c>
-      <c r="F71" s="56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="56" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>SBA</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
         <is>
           <t>Jun 30, 2026</t>
         </is>
       </c>
-      <c r="H71" s="56" t="inlineStr">
+      <c r="H72" s="17" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="I71" s="56" t="inlineStr">
+      <c r="I72" s="17" t="inlineStr">
         <is>
           <t>Special Notice</t>
         </is>
       </c>
-      <c r="J71" s="18" t="inlineStr">
+      <c r="J72" s="18" t="inlineStr">
         <is>
           <t>🔴 Urgent</t>
         </is>
       </c>
-      <c r="K71" s="57" t="inlineStr">
+      <c r="K72" s="42" t="inlineStr">
         <is>
           <t>SAM.gov ↗</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:K71"/>
+  <autoFilter ref="B5:K72"/>
   <mergeCells count="2">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="B2:K2"/>
@@ -19635,6 +19913,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
